--- a/src/attributions/attributions_saliency_traj_314.xlsx
+++ b/src/attributions/attributions_saliency_traj_314.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03843984380364418</v>
+        <v>0.01747889816761017</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01323898881673813</v>
+        <v>0.01077310554683208</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01617333479225636</v>
+        <v>0.02303148806095123</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02085823565721512</v>
+        <v>0.1164887249469757</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007845416665077209</v>
+        <v>0.01044644508510828</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0143523970618844</v>
+        <v>0.0008217748254537582</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003396572079509497</v>
+        <v>0.03963524475693703</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008995646610856056</v>
+        <v>0.005921144969761372</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002075013937428594</v>
+        <v>0.001368578057736158</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0361754521727562</v>
+        <v>0.01338348723948002</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009488951414823532</v>
+        <v>0.005676067434251308</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01554619055241346</v>
+        <v>0.02885674871504307</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003943065647035837</v>
+        <v>0.1517922431230545</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0005794183816760778</v>
+        <v>0.02053739130496979</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0007322384044528008</v>
+        <v>0.02493993565440178</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003158858511596918</v>
+        <v>0.03574402257800102</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002400386612862349</v>
+        <v>0.02449284307658672</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002782452618703246</v>
+        <v>0.004406000021845102</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003645821241661906</v>
+        <v>0.000235212966799736</v>
       </c>
       <c r="T2" t="n">
-        <v>0.009955103509128094</v>
+        <v>0.0004915363388136029</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005318567156791687</v>
+        <v>0.0008109036134555936</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002795458305627108</v>
+        <v>0.01460006553679705</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00506629841402173</v>
+        <v>0.008062519133090973</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004995477851480246</v>
+        <v>0.02226253971457481</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001821290352381766</v>
+        <v>0.004366576671600342</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.007590508088469505</v>
+        <v>0.002996885217726231</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001143810455687344</v>
+        <v>0.001684797462075949</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0003527849912643433</v>
+        <v>0.009938633069396019</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.01406787242740393</v>
+        <v>0.01543041970580816</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.002202674048021436</v>
+        <v>0.003444153815507889</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.006664657033979893</v>
+        <v>0.00310127716511488</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.004457694943994284</v>
+        <v>0.01246598642319441</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001626464072614908</v>
+        <v>0.02349343523383141</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.001427152194082737</v>
+        <v>0.01230283547192812</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.004334175959229469</v>
+        <v>0.01506427582353354</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.004888238850980997</v>
+        <v>0.02719631418585777</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.003893252462148666</v>
+        <v>0.003663036972284317</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.002798520028591156</v>
+        <v>0.01895583607256413</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0009327690349891782</v>
+        <v>0.003337489906698465</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.00376084866002202</v>
+        <v>0.02002740651369095</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.00869700126349926</v>
+        <v>0.006998276803642511</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.001621587434783578</v>
+        <v>0.007073964923620224</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.005768075585365295</v>
+        <v>0.02039686404168606</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.008382201194763184</v>
+        <v>0.004186919424682856</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.00372821930795908</v>
+        <v>0.002599491039291024</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.02307058311998844</v>
+        <v>0.007695472799241543</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.008894016966223717</v>
+        <v>0.004538542591035366</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.01469914801418781</v>
+        <v>0.003487800713628531</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.01351303979754448</v>
+        <v>0.06183379888534546</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.6564731746912e-05</v>
+        <v>0.04294157773256302</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.002603190951049328</v>
+        <v>0.001130204182118177</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.004778929520398378</v>
+        <v>0.005453602410852909</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.007326201535761356</v>
+        <v>0.01462801638990641</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.005980851594358683</v>
+        <v>0.01252533122897148</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0203967597335577</v>
+        <v>0.02854176051914692</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.02186550199985504</v>
+        <v>0.01067462097853422</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.000343147199600935</v>
+        <v>0.008243163116276264</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.006568740587681532</v>
+        <v>0.01111237797886133</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.01302941050380468</v>
+        <v>0.0179083775728941</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.001732308650389314</v>
+        <v>0.005059569142758846</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.004115620627999306</v>
+        <v>0.02254102006554604</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.009605514816939831</v>
+        <v>0.0104560824111104</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.009308422915637493</v>
+        <v>0.03298038616776466</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0002594740362837911</v>
+        <v>0.005409164819866419</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.004736357368528843</v>
+        <v>0.009599888697266579</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.003435090882703662</v>
+        <v>0.01078971102833748</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.006419611629098654</v>
+        <v>0.02028722502291203</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.007172419223934412</v>
+        <v>0.02754208073019981</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.002079492434859276</v>
+        <v>0.004357410594820976</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.005696312990039587</v>
+        <v>0.006544644944369793</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.00718484865501523</v>
+        <v>0.005772113800048828</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.004333256278187037</v>
+        <v>0.01026658527553082</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.008117635734379292</v>
+        <v>0.003496652934700251</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0002502677962183952</v>
+        <v>0.002494107466191053</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.007169566117227077</v>
+        <v>0.002056138357147574</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.00154696183744818</v>
+        <v>0.05682910978794098</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.00407625176012516</v>
+        <v>0.0204474963247776</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0009927479550242424</v>
+        <v>0.01570747792720795</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.002575140912085772</v>
+        <v>0.002933438634499907</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.00498069217428565</v>
+        <v>0.003622430842369795</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.003841697704046965</v>
+        <v>0.007353533059358597</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.007030873093754053</v>
+        <v>0.004333939403295517</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.004095092415809631</v>
+        <v>0.0120827266946435</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.001315933535806835</v>
+        <v>0.0002528660697862506</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.789488644339144e-05</v>
+        <v>0.03927906602621078</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.002120001474395394</v>
+        <v>0.003963875584304333</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.005431320983916521</v>
+        <v>0.01093207113444805</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0001271277433261275</v>
+        <v>0.0004200915573164821</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.004955691751092672</v>
+        <v>0.01082913298159838</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0005197172868065536</v>
+        <v>0.002970523433759809</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.01181982737034559</v>
+        <v>0.006686084903776646</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.00852541346102953</v>
+        <v>0.008455093950033188</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0003080336609855294</v>
+        <v>0.02265353128314018</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.01144429389387369</v>
+        <v>0.05430988967418671</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.01388132758438587</v>
+        <v>0.03010956943035126</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.005795470904558897</v>
+        <v>0.01980235613882542</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.008980205282568932</v>
+        <v>0.004490863066166639</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.01508005149662495</v>
+        <v>0.01231510378420353</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.002679453231394291</v>
+        <v>0.02600536122918129</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.00563362892717123</v>
+        <v>0.003935069777071476</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.004025721456855536</v>
+        <v>0.01150024961680174</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.002134133595973253</v>
+        <v>0.001512938644737005</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.001826522871851921</v>
+        <v>0.04294746741652489</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.001620020717382431</v>
+        <v>0.006708812899887562</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.00444356445223093</v>
+        <v>0.004585839807987213</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0004641470732167363</v>
+        <v>0.002859383355826139</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.00340137560851872</v>
+        <v>0.009307842701673508</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.0005271825939416885</v>
+        <v>0.0002130822977051139</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.002043898217380047</v>
+        <v>0.003130785189568996</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.01261226832866669</v>
+        <v>0.01398291438817978</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.01787108927965164</v>
+        <v>0.01777482032775879</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01662221178412437</v>
+        <v>0.02170844748616219</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.01526900287717581</v>
+        <v>0.009497735649347305</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.01167500484734774</v>
+        <v>0.0249747522175312</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.001449077390134335</v>
+        <v>0.008328474126756191</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.02023353241384029</v>
+        <v>0.0468493327498436</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.00472703343257308</v>
+        <v>0.0008447621949017048</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.005635625682771206</v>
+        <v>0.007038259878754616</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.002088978420943022</v>
+        <v>0.01451902464032173</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.005563756451010704</v>
+        <v>0.02517661638557911</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.007854277268052101</v>
+        <v>0.01530477218329906</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.006860219873487949</v>
+        <v>0.01263853628188372</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0006314087077043951</v>
+        <v>0.006087184883654118</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.003647912759333849</v>
+        <v>0.01125567965209484</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.002600267063826323</v>
+        <v>0.006569766905158758</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.007592819631099701</v>
+        <v>0.02841337770223618</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.006505510769784451</v>
+        <v>0.0002130865468643606</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.0004781830357387662</v>
+        <v>0.003961786162108183</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.004016119986772537</v>
+        <v>0.05373983830213547</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.001412394223734736</v>
+        <v>0.003879307769238949</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.001117025967687368</v>
+        <v>0.001104494091123343</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.004113777540624142</v>
+        <v>0.01327222771942616</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.001790514215826988</v>
+        <v>0.007656613364815712</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.001551507855765522</v>
+        <v>0.04098642617464066</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.004288631025701761</v>
+        <v>0.02672651596367359</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.008632989600300789</v>
+        <v>0.0192557331174612</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.007950715720653534</v>
+        <v>0.003962685354053974</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.007214155979454517</v>
+        <v>0.002890186849981546</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.009054224006831646</v>
+        <v>0.04216653853654861</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.004834805149585009</v>
+        <v>0.01077424548566341</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.0006196009926497936</v>
+        <v>0.008767332881689072</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.001178139820694923</v>
+        <v>0.005095215514302254</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.002094823634251952</v>
+        <v>0.005548933055251837</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.001684550661593676</v>
+        <v>0.0003506719367578626</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.000158277340233326</v>
+        <v>0.009597179479897022</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.009905477985739708</v>
+        <v>0.01366566680371761</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.001378190936520696</v>
+        <v>0.01352440379559994</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.0002187860663980246</v>
+        <v>0.041361965239048</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.001789367059245706</v>
+        <v>0.003770327661186457</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.004556169733405113</v>
+        <v>0.02350186556577682</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.002656220924109221</v>
+        <v>0.01305193826556206</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.007704672869294882</v>
+        <v>0.009194488637149334</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.01083090715110302</v>
+        <v>0.01321485918015242</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.005546957720071077</v>
+        <v>0.002482621930539608</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.004419134929776192</v>
+        <v>0.008097868412733078</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.00278048194013536</v>
+        <v>0.002326120622456074</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.001826447900384665</v>
+        <v>0.04739946871995926</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.001363181509077549</v>
+        <v>0.003506748005747795</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.003490046132355928</v>
+        <v>0.001512117101810873</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.001466130255721509</v>
+        <v>0.00381161761470139</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.003505526809021831</v>
+        <v>0.01102236285805702</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.001293778419494629</v>
+        <v>0.0001464965753257275</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.001202465035021305</v>
+        <v>0.005615923553705215</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.006485786754637957</v>
+        <v>0.0004222887509968132</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.01002630777657032</v>
+        <v>0.009245061315596104</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.00336409593001008</v>
+        <v>0.02255389839410782</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.005117880180478096</v>
+        <v>0.0194985643029213</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.01049344800412655</v>
+        <v>0.004650138318538666</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.004241954069584608</v>
+        <v>0.0002833954058587551</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.001226512249559164</v>
+        <v>0.0130903385579586</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.004858248401433229</v>
+        <v>0.0102750463411212</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.004903557244688272</v>
+        <v>0.01838553883135319</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.01313498057425022</v>
+        <v>0.03509767353534698</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.009135976433753967</v>
+        <v>0.01455662399530411</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.009769799187779427</v>
+        <v>0.03195703029632568</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.01091911271214485</v>
+        <v>0.003978074062615633</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.007717499975115061</v>
+        <v>0.03624894097447395</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.003418408799916506</v>
+        <v>0.002937962301075459</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.00155161670409143</v>
+        <v>0.02801401354372501</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.001151800737716258</v>
+        <v>0.005183123983442783</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.003109816461801529</v>
+        <v>0.006016570143401623</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.006882686167955399</v>
+        <v>0.005351732950657606</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0004954044707119465</v>
+        <v>0.009093147702515125</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0008437996730208397</v>
+        <v>0.0415918156504631</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.007029721047729254</v>
+        <v>0.0114256301894784</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.001486073946580291</v>
+        <v>0.01399309560656548</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.009169257245957851</v>
+        <v>0.02943341247737408</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.002987089799717069</v>
+        <v>0.002711141714826226</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.006444206926971674</v>
+        <v>0.004659784957766533</v>
       </c>
     </row>
     <row r="3">
@@ -2706,3416 +2706,3416 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.960846126778051e-06</v>
+        <v>8.736112278029395e-08</v>
       </c>
       <c r="B5" t="n">
-        <v>3.770904004340991e-05</v>
+        <v>2.880407237171312e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>3.677904942378518e-06</v>
+        <v>2.958628897431481e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.22545913857175e-05</v>
+        <v>1.708496029095841e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>9.02488682186231e-06</v>
+        <v>5.356926902067016e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>8.858452929416671e-06</v>
+        <v>1.598856727014208e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.240077267539164e-07</v>
+        <v>2.385070807520151e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.25680706636922e-07</v>
+        <v>6.735010060765489e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.256588348041987e-06</v>
+        <v>2.546661193036925e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.427773536823224e-06</v>
+        <v>2.040388658031134e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.022283999598585e-05</v>
+        <v>3.008631210832391e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.136600642188569e-06</v>
+        <v>2.595660220094942e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.647236058488488e-05</v>
+        <v>2.795402167521388e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.012018674373394e-05</v>
+        <v>1.102176625522588e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.525321295048343e-05</v>
+        <v>1.674982001986791e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>4.772035936184693e-06</v>
+        <v>2.333318960268116e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.68224799685413e-06</v>
+        <v>1.86382784761463e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.579355620786373e-07</v>
+        <v>2.761749584578865e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.825615628258674e-07</v>
+        <v>3.334285736400489e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.98676672577858e-06</v>
+        <v>2.162108536651886e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.133140004749293e-07</v>
+        <v>4.358610539156871e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.766540430660825e-06</v>
+        <v>8.641642956774831e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.197766295035763e-07</v>
+        <v>6.922989115309974e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.798491434281459e-06</v>
+        <v>3.312963414714432e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.63647165815928e-06</v>
+        <v>7.869368090496209e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.558605724014342e-06</v>
+        <v>5.552586301860174e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.064424840384163e-06</v>
+        <v>1.191310605719309e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.277246039739111e-06</v>
+        <v>2.043124780470862e-08</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.516600036666205e-06</v>
+        <v>7.120207357047548e-08</v>
       </c>
       <c r="AD5" t="n">
-        <v>7.847686447348678e-07</v>
+        <v>2.336923543566627e-08</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.498835272035649e-07</v>
+        <v>6.824453890885707e-08</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.484514862379001e-07</v>
+        <v>4.657669450125468e-08</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.170927579456475e-07</v>
+        <v>7.980073490898576e-08</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.399560915160691e-06</v>
+        <v>1.334377053296976e-09</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.783439413178712e-06</v>
+        <v>9.915778775848594e-08</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.824632022362493e-06</v>
+        <v>1.755881662290903e-08</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.667645730980439e-06</v>
+        <v>2.95905309144473e-08</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.350123163021635e-06</v>
+        <v>3.518958280324114e-08</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.458534825360402e-06</v>
+        <v>1.146775758797958e-07</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.031130735413171e-07</v>
+        <v>6.295484666907214e-08</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.108139369738637e-06</v>
+        <v>5.005411907177404e-08</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.511512881639646e-07</v>
+        <v>6.619352177494875e-08</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.937239858307294e-06</v>
+        <v>1.865097409847749e-08</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.334272034611786e-07</v>
+        <v>1.21136487507556e-08</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.847966698027449e-06</v>
+        <v>1.414009531686133e-08</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.981089664899628e-06</v>
+        <v>2.139654142752079e-08</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.374245741521008e-05</v>
+        <v>1.902071176118625e-07</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.478572926316701e-06</v>
+        <v>1.289891002898003e-07</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.861648322839756e-06</v>
+        <v>3.518907831789875e-09</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.618900675268378e-06</v>
+        <v>2.684354853954574e-07</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.113909888772469e-06</v>
+        <v>1.844003350015555e-07</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.6258041998517e-06</v>
+        <v>5.864569274649511e-09</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.005012674999307e-06</v>
+        <v>4.916285689660072e-08</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.743455974676181e-06</v>
+        <v>3.149263516633027e-09</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.365689281054074e-06</v>
+        <v>2.502002871551667e-08</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.982603397569619e-06</v>
+        <v>9.705944137294864e-08</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.0383791050117e-05</v>
+        <v>2.608206628451626e-08</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.553629545014701e-06</v>
+        <v>1.108308680386472e-07</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.023469490581192e-06</v>
+        <v>1.735295143134863e-07</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.41514964425005e-06</v>
+        <v>4.451760560186813e-08</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.106153942804667e-06</v>
+        <v>4.958957333656144e-08</v>
       </c>
       <c r="BJ5" t="n">
-        <v>7.714689672866371e-06</v>
+        <v>1.220214613795179e-07</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.668216782491072e-06</v>
+        <v>1.619902767480141e-09</v>
       </c>
       <c r="BL5" t="n">
-        <v>2.821757561832783e-06</v>
+        <v>3.123897585055602e-08</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.11115695189801e-06</v>
+        <v>3.920222724218547e-08</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.609927600540686e-06</v>
+        <v>7.432521265116065e-10</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.83918996299326e-06</v>
+        <v>2.60574246624401e-08</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.24140762333991e-06</v>
+        <v>9.843095227779486e-08</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.720970885799034e-06</v>
+        <v>3.216880761769403e-09</v>
       </c>
       <c r="BR5" t="n">
-        <v>1.976567773454008e-06</v>
+        <v>1.148285821983563e-08</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.853002100295271e-07</v>
+        <v>4.82794355605165e-08</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.851209496337106e-07</v>
+        <v>1.038685315535304e-08</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.845699320161657e-07</v>
+        <v>2.622507899729953e-08</v>
       </c>
       <c r="BV5" t="n">
-        <v>1.234689989360049e-05</v>
+        <v>6.93460009415503e-08</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.908603957825107e-06</v>
+        <v>6.138127872645782e-08</v>
       </c>
       <c r="BX5" t="n">
-        <v>6.455552465922665e-06</v>
+        <v>3.744037524455734e-09</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.211960466207529e-06</v>
+        <v>5.217075127461612e-08</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.047182306341711e-06</v>
+        <v>7.819581071544235e-08</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.41340807810775e-06</v>
+        <v>7.730822915164026e-08</v>
       </c>
       <c r="CB5" t="n">
-        <v>7.699625257373555e-07</v>
+        <v>1.181228181934557e-08</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.364997610333376e-06</v>
+        <v>3.785691760072041e-10</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.932548059357941e-07</v>
+        <v>1.863892151732216e-08</v>
       </c>
       <c r="CE5" t="n">
-        <v>5.803048225061502e-06</v>
+        <v>1.039435915117792e-07</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.770391003854456e-06</v>
+        <v>1.90060811533499e-09</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.374674522798159e-06</v>
+        <v>5.633278732375402e-08</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.37819813517126e-06</v>
+        <v>2.081129046871411e-08</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.489689450158039e-06</v>
+        <v>2.900127071825409e-08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>5.146405896994111e-07</v>
+        <v>1.750161082725299e-08</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.054796131138573e-07</v>
+        <v>4.459071334395048e-09</v>
       </c>
       <c r="CL5" t="n">
-        <v>3.154354089929257e-06</v>
+        <v>1.52109507212117e-08</v>
       </c>
       <c r="CM5" t="n">
-        <v>6.739620857842965e-06</v>
+        <v>7.182743644307266e-08</v>
       </c>
       <c r="CN5" t="n">
-        <v>3.366150735928386e-08</v>
+        <v>1.456067906246972e-07</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.800548261599033e-06</v>
+        <v>1.375723570617993e-07</v>
       </c>
       <c r="CP5" t="n">
-        <v>5.089555997983553e-06</v>
+        <v>1.185867191111356e-07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.605204028644948e-06</v>
+        <v>1.179937392237207e-08</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.674414513938245e-07</v>
+        <v>1.457688192374462e-08</v>
       </c>
       <c r="CS5" t="n">
-        <v>6.89402304487885e-06</v>
+        <v>8.221680225517503e-09</v>
       </c>
       <c r="CT5" t="n">
-        <v>4.523672032519244e-06</v>
+        <v>7.727488338105104e-08</v>
       </c>
       <c r="CU5" t="n">
-        <v>8.598780141255702e-07</v>
+        <v>4.088341043484434e-08</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.813898791169777e-07</v>
+        <v>2.992788239453148e-08</v>
       </c>
       <c r="CW5" t="n">
-        <v>5.475403213495156e-06</v>
+        <v>9.830229430463078e-08</v>
       </c>
       <c r="CX5" t="n">
-        <v>3.616146386775654e-06</v>
+        <v>8.288234099040892e-09</v>
       </c>
       <c r="CY5" t="n">
-        <v>4.497662303037941e-06</v>
+        <v>7.062336493390831e-08</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.397714299855579e-06</v>
+        <v>3.124268488363668e-08</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.681140131244319e-06</v>
+        <v>3.509097723508603e-08</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.114619976760878e-06</v>
+        <v>2.327608328300812e-08</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.492758087806578e-06</v>
+        <v>8.100617954198697e-09</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.295358854098595e-06</v>
+        <v>1.05938902095204e-08</v>
       </c>
       <c r="DE5" t="n">
-        <v>4.049271410622168e-06</v>
+        <v>4.326853542124809e-08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.488367843194283e-06</v>
+        <v>1.210888278535549e-08</v>
       </c>
       <c r="DG5" t="n">
-        <v>6.850230874988483e-06</v>
+        <v>4.117941543313464e-08</v>
       </c>
       <c r="DH5" t="n">
-        <v>1.720340696920175e-05</v>
+        <v>1.955497097583248e-08</v>
       </c>
       <c r="DI5" t="n">
-        <v>2.677160864550387e-06</v>
+        <v>2.638934226695255e-08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.855351340258494e-06</v>
+        <v>1.078473346183273e-07</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.67170526310656e-06</v>
+        <v>2.292862433250775e-08</v>
       </c>
       <c r="DL5" t="n">
-        <v>4.013090801890939e-06</v>
+        <v>9.892612240491871e-08</v>
       </c>
       <c r="DM5" t="n">
-        <v>6.3706642094985e-07</v>
+        <v>4.294647837355114e-08</v>
       </c>
       <c r="DN5" t="n">
-        <v>2.294558498761035e-06</v>
+        <v>7.6200219467637e-09</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.269199512738851e-06</v>
+        <v>3.891864963634362e-08</v>
       </c>
       <c r="DP5" t="n">
-        <v>3.455523028605967e-06</v>
+        <v>4.158632549433605e-09</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1.344927511581773e-07</v>
+        <v>5.025713534223542e-08</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.614709597371984e-07</v>
+        <v>6.214093239975682e-09</v>
       </c>
       <c r="DS5" t="n">
-        <v>2.593476210677181e-06</v>
+        <v>1.644185765314887e-08</v>
       </c>
       <c r="DT5" t="n">
-        <v>2.865771193683031e-07</v>
+        <v>5.789323154203885e-08</v>
       </c>
       <c r="DU5" t="n">
-        <v>1.23773725135834e-06</v>
+        <v>5.230727495586507e-08</v>
       </c>
       <c r="DV5" t="n">
-        <v>5.720733497582842e-06</v>
+        <v>8.475438129096347e-09</v>
       </c>
       <c r="DW5" t="n">
-        <v>3.850345819955692e-08</v>
+        <v>9.719123283957742e-10</v>
       </c>
       <c r="DX5" t="n">
-        <v>6.686791039101081e-06</v>
+        <v>2.88693797756423e-08</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.398586381488713e-06</v>
+        <v>5.482198162098939e-08</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1.656207814448862e-06</v>
+        <v>4.985545132285552e-08</v>
       </c>
       <c r="EA5" t="n">
-        <v>1.949954139490728e-06</v>
+        <v>7.131944812499569e-08</v>
       </c>
       <c r="EB5" t="n">
-        <v>5.050663276051637e-06</v>
+        <v>8.657808692191793e-09</v>
       </c>
       <c r="EC5" t="n">
-        <v>8.053686997300247e-07</v>
+        <v>1.927605808305088e-08</v>
       </c>
       <c r="ED5" t="n">
-        <v>1.244132590727531e-06</v>
+        <v>1.106510509885084e-07</v>
       </c>
       <c r="EE5" t="n">
-        <v>1.448979105589387e-06</v>
+        <v>7.172027949309268e-08</v>
       </c>
       <c r="EF5" t="n">
-        <v>2.113519713020651e-06</v>
+        <v>4.925760066498697e-08</v>
       </c>
       <c r="EG5" t="n">
-        <v>3.385076297490741e-06</v>
+        <v>2.986371328006499e-08</v>
       </c>
       <c r="EH5" t="n">
-        <v>1.881440994111472e-06</v>
+        <v>4.360915539791677e-08</v>
       </c>
       <c r="EI5" t="n">
-        <v>2.320497742402949e-06</v>
+        <v>4.76046224662241e-08</v>
       </c>
       <c r="EJ5" t="n">
-        <v>1.11442875549983e-06</v>
+        <v>2.272143007076011e-08</v>
       </c>
       <c r="EK5" t="n">
-        <v>2.305474708919064e-06</v>
+        <v>2.678971711134182e-08</v>
       </c>
       <c r="EL5" t="n">
-        <v>7.673214668102446e-07</v>
+        <v>4.181718793461187e-08</v>
       </c>
       <c r="EM5" t="n">
-        <v>1.708734998828731e-06</v>
+        <v>1.256679649230819e-08</v>
       </c>
       <c r="EN5" t="n">
-        <v>1.498854203418887e-06</v>
+        <v>5.69675684403137e-09</v>
       </c>
       <c r="EO5" t="n">
-        <v>1.772875748429215e-07</v>
+        <v>1.697012663726127e-08</v>
       </c>
       <c r="EP5" t="n">
-        <v>2.486647190380609e-06</v>
+        <v>7.725827089188897e-08</v>
       </c>
       <c r="EQ5" t="n">
-        <v>4.557360171020264e-06</v>
+        <v>5.754736243090974e-09</v>
       </c>
       <c r="ER5" t="n">
-        <v>5.864868626304087e-07</v>
+        <v>2.00842507069865e-08</v>
       </c>
       <c r="ES5" t="n">
-        <v>2.939122623502044e-06</v>
+        <v>2.532936349552983e-08</v>
       </c>
       <c r="ET5" t="n">
-        <v>1.954978415596997e-06</v>
+        <v>1.968500029647657e-08</v>
       </c>
       <c r="EU5" t="n">
-        <v>2.67496920969279e-06</v>
+        <v>3.557005801013702e-09</v>
       </c>
       <c r="EV5" t="n">
-        <v>6.993838724156376e-06</v>
+        <v>4.610649639857911e-08</v>
       </c>
       <c r="EW5" t="n">
-        <v>1.319096327279112e-06</v>
+        <v>4.587503710240526e-08</v>
       </c>
       <c r="EX5" t="n">
-        <v>7.166408977354877e-07</v>
+        <v>2.013023703284489e-08</v>
       </c>
       <c r="EY5" t="n">
-        <v>5.281488029140746e-06</v>
+        <v>1.090136123593766e-07</v>
       </c>
       <c r="EZ5" t="n">
-        <v>3.102430355284014e-06</v>
+        <v>6.301966060107134e-09</v>
       </c>
       <c r="FA5" t="n">
-        <v>3.013596142409369e-06</v>
+        <v>7.234972088099312e-08</v>
       </c>
       <c r="FB5" t="n">
-        <v>4.739530936603842e-07</v>
+        <v>1.365633384153853e-09</v>
       </c>
       <c r="FC5" t="n">
-        <v>2.445463223921251e-06</v>
+        <v>1.61903077611214e-08</v>
       </c>
       <c r="FD5" t="n">
-        <v>1.653887807151477e-06</v>
+        <v>5.101104871840789e-09</v>
       </c>
       <c r="FE5" t="n">
-        <v>4.738805330362084e-07</v>
+        <v>2.106748020480609e-08</v>
       </c>
       <c r="FF5" t="n">
-        <v>3.252557007726864e-06</v>
+        <v>6.437593125241392e-09</v>
       </c>
       <c r="FG5" t="n">
-        <v>3.086077867919812e-06</v>
+        <v>1.640358959775767e-08</v>
       </c>
       <c r="FH5" t="n">
-        <v>1.87978844223835e-06</v>
+        <v>5.646702305739382e-08</v>
       </c>
       <c r="FI5" t="n">
-        <v>5.336627509677783e-06</v>
+        <v>1.217138745346347e-08</v>
       </c>
       <c r="FJ5" t="n">
-        <v>3.483063437670353e-06</v>
+        <v>6.83657646050051e-08</v>
       </c>
       <c r="FK5" t="n">
-        <v>1.042980102283764e-07</v>
+        <v>1.514027125892881e-08</v>
       </c>
       <c r="FL5" t="n">
-        <v>2.374918040004559e-06</v>
+        <v>3.837566708853046e-09</v>
       </c>
       <c r="FM5" t="n">
-        <v>4.457896238818648e-07</v>
+        <v>4.125081431993749e-08</v>
       </c>
       <c r="FN5" t="n">
-        <v>5.773540578957181e-06</v>
+        <v>3.926733072034949e-08</v>
       </c>
       <c r="FO5" t="n">
-        <v>1.578920205247414e-06</v>
+        <v>1.203590471732241e-07</v>
       </c>
       <c r="FP5" t="n">
-        <v>1.333372097178653e-06</v>
+        <v>3.959550554100133e-08</v>
       </c>
       <c r="FQ5" t="n">
-        <v>1.239564539901039e-06</v>
+        <v>1.383300087809403e-07</v>
       </c>
       <c r="FR5" t="n">
-        <v>1.8701825865719e-06</v>
+        <v>8.516934713043156e-08</v>
       </c>
       <c r="FS5" t="n">
-        <v>2.345078087273578e-08</v>
+        <v>3.182935159884437e-08</v>
       </c>
       <c r="FT5" t="n">
-        <v>9.832265277509578e-06</v>
+        <v>1.26820296486585e-07</v>
       </c>
       <c r="FU5" t="n">
-        <v>1.368222797282215e-06</v>
+        <v>9.802674583170301e-08</v>
       </c>
       <c r="FV5" t="n">
-        <v>2.201373490606784e-06</v>
+        <v>6.010078124063511e-08</v>
       </c>
       <c r="FW5" t="n">
-        <v>3.264102815592196e-06</v>
+        <v>3.567096840129125e-08</v>
       </c>
       <c r="FX5" t="n">
-        <v>2.452507487760158e-06</v>
+        <v>1.961229045832624e-08</v>
       </c>
       <c r="FY5" t="n">
-        <v>5.620461706712376e-06</v>
+        <v>1.744977851103613e-08</v>
       </c>
       <c r="FZ5" t="n">
-        <v>2.12833947443869e-06</v>
+        <v>2.032943591245839e-08</v>
       </c>
       <c r="GA5" t="n">
-        <v>6.287594089826598e-08</v>
+        <v>7.9863170299177e-08</v>
       </c>
       <c r="GB5" t="n">
-        <v>1.917894394409814e-07</v>
+        <v>4.081921289866841e-08</v>
       </c>
       <c r="GC5" t="n">
-        <v>4.713547696155729e-06</v>
+        <v>7.07890563944602e-08</v>
       </c>
       <c r="GD5" t="n">
-        <v>4.161937795288395e-06</v>
+        <v>9.022605951258811e-08</v>
       </c>
       <c r="GE5" t="n">
-        <v>8.625209375168197e-06</v>
+        <v>8.981365340332559e-08</v>
       </c>
       <c r="GF5" t="n">
-        <v>1.448223656552727e-06</v>
+        <v>1.704276053615672e-09</v>
       </c>
       <c r="GG5" t="n">
-        <v>4.496653218666324e-06</v>
+        <v>4.663635522206278e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7.848990935599431e-05</v>
+        <v>8.504206453624485e-13</v>
       </c>
       <c r="B6" t="n">
-        <v>0.004697104915976524</v>
+        <v>2.459458635015177e-12</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002314612647751346</v>
+        <v>1.96971367168175e-12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001563393976539373</v>
+        <v>1.222853849430772e-12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001919884351082146</v>
+        <v>2.404261685573506e-12</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001838164404034615</v>
+        <v>3.242827881222432e-12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002330934221390635</v>
+        <v>2.845871975576397e-12</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0007283767336048186</v>
+        <v>5.70745360695124e-12</v>
       </c>
       <c r="I6" t="n">
-        <v>4.935516335535794e-05</v>
+        <v>5.669192979645965e-12</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004040580824948847</v>
+        <v>5.927802736518939e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004459447227418423</v>
+        <v>8.488162429876045e-13</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0003465893678367138</v>
+        <v>2.209009884734936e-12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001091737765818834</v>
+        <v>4.643372492063591e-12</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001429609372280538</v>
+        <v>3.333760784790529e-12</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002266941824927926</v>
+        <v>2.189254853790512e-12</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0003430374199524522</v>
+        <v>1.478991896401022e-13</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0003473485703580081</v>
+        <v>7.857821164580781e-12</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003894786641467363</v>
+        <v>2.326510728858922e-12</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001358884037472308</v>
+        <v>2.318504112655551e-12</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005999573622830212</v>
+        <v>2.716296371857441e-12</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001803902559913695</v>
+        <v>6.483723063652191e-13</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0004499268834479153</v>
+        <v>4.899493896530493e-13</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0002736335736699402</v>
+        <v>2.943606187792713e-13</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0004824849020224065</v>
+        <v>8.07195456309362e-13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.668024196987972e-05</v>
+        <v>9.297629940258068e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002991678775288165</v>
+        <v>1.410786309823109e-12</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001824204227887094</v>
+        <v>3.331354506488915e-12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0002326964458916336</v>
+        <v>3.599720565031217e-12</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.841104136081412e-05</v>
+        <v>1.980099027451554e-13</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0005731799174100161</v>
+        <v>1.689664250528744e-12</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0002880983520299196</v>
+        <v>2.761301387196879e-13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0001802080514607951</v>
+        <v>1.734822138374503e-13</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.214381285943091e-05</v>
+        <v>2.415484695941772e-12</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.000123937294119969</v>
+        <v>1.958978769131536e-13</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0003521319886203855</v>
+        <v>1.193714831843051e-12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0005525387241505086</v>
+        <v>2.791936820623064e-12</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0004458644834812731</v>
+        <v>2.00382202150684e-12</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0006447138730436563</v>
+        <v>1.237962531965009e-12</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0002857621584553272</v>
+        <v>3.258199265943063e-12</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.450936856097542e-05</v>
+        <v>1.854831663695294e-13</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.245593688916415e-06</v>
+        <v>1.89664148102231e-12</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.000395533163100481</v>
+        <v>3.162018986490461e-13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0001305735640926287</v>
+        <v>1.021755163116422e-12</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0002192128304159269</v>
+        <v>3.768483355232055e-12</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0003097328881267458</v>
+        <v>1.247142363339226e-12</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.000333363888785243</v>
+        <v>3.835367895672903e-13</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.003182615386322141</v>
+        <v>5.005468695779003e-12</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.0003864712780341506</v>
+        <v>2.520682230652826e-12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0002641796891111881</v>
+        <v>1.57871952273167e-13</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.365249201830011e-05</v>
+        <v>3.298852293762145e-12</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0004118328506592661</v>
+        <v>1.779080029996882e-12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.000134295187308453</v>
+        <v>7.914177126144839e-13</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0004123685939703137</v>
+        <v>1.249102709287297e-12</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.930991806555539e-05</v>
+        <v>3.207013105598067e-14</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0001057454792317003</v>
+        <v>6.295634586567234e-12</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0008944095461629331</v>
+        <v>6.134106243782522e-12</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0006433956441469491</v>
+        <v>2.28685343231505e-12</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0001300699805142358</v>
+        <v>3.202250097034121e-12</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.001825488172471523</v>
+        <v>6.192107590563545e-12</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.001394240185618401</v>
+        <v>2.349323643610624e-12</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.000483026058645919</v>
+        <v>7.11381040879866e-13</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0002273624122608453</v>
+        <v>3.353431031125065e-12</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.852190174162388e-05</v>
+        <v>1.001242231485344e-11</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0005408841534517705</v>
+        <v>7.220876457533776e-13</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.000539666973054409</v>
+        <v>1.564225745459558e-12</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0003420652647037059</v>
+        <v>9.933336705264528e-13</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0001029695267789066</v>
+        <v>1.500921999533777e-12</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0004902959335595369</v>
+        <v>8.686154009604485e-13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0003875484107993543</v>
+        <v>6.22934998939853e-14</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0002600915031507611</v>
+        <v>1.34269797971015e-12</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0001714697282295674</v>
+        <v>7.65733288408954e-13</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0003293939225841314</v>
+        <v>1.49936779571952e-12</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0002354987227590755</v>
+        <v>3.67317721378102e-12</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.001720362808555365</v>
+        <v>3.378991314181845e-12</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0003350256592966616</v>
+        <v>7.253940286985894e-13</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0003445131878834218</v>
+        <v>1.691436162139237e-12</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.374738298589364e-06</v>
+        <v>9.47884565977164e-13</v>
       </c>
       <c r="BZ6" t="n">
-        <v>9.028289059642702e-05</v>
+        <v>2.803101717754886e-13</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.138526178896427e-05</v>
+        <v>9.938243804297198e-13</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0001570449821883813</v>
+        <v>2.231242534483924e-13</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0001655405649216846</v>
+        <v>1.06165532094693e-12</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.870621392503381e-05</v>
+        <v>6.375906204912629e-13</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0008078744285739958</v>
+        <v>5.230899264088706e-13</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0001724441826809198</v>
+        <v>1.537659295681656e-13</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0003326060832478106</v>
+        <v>1.450788274237613e-13</v>
       </c>
       <c r="CH6" t="n">
-        <v>6.588920950889587e-05</v>
+        <v>1.133227626320954e-12</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.000268264178885147</v>
+        <v>8.533852877828929e-13</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0003959050518460572</v>
+        <v>2.955299308222969e-14</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0001023820586851798</v>
+        <v>1.99275600361315e-13</v>
       </c>
       <c r="CL6" t="n">
-        <v>6.417458644136786e-05</v>
+        <v>2.500356150424154e-13</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0009393998188897967</v>
+        <v>5.600799771882103e-13</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0004457730101421475</v>
+        <v>1.268735767487317e-12</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.041983705363236e-05</v>
+        <v>3.078310609888613e-12</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0005549558554776013</v>
+        <v>2.941330555852883e-12</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0005298240575939417</v>
+        <v>3.611835873787439e-12</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0001627148303668946</v>
+        <v>2.821245407430562e-12</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0009976556757465005</v>
+        <v>3.234080754935253e-12</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0008850981248542666</v>
+        <v>9.124103382551763e-13</v>
       </c>
       <c r="CU6" t="n">
-        <v>4.20059914176818e-05</v>
+        <v>2.933421084164167e-12</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.727818016661331e-06</v>
+        <v>1.352348951138421e-13</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0007404923089779913</v>
+        <v>3.907734595978707e-13</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0002105844032485038</v>
+        <v>5.455335076905155e-13</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0004847095697186887</v>
+        <v>5.038932595832768e-13</v>
       </c>
       <c r="CZ6" t="n">
-        <v>3.428659329074435e-05</v>
+        <v>1.365047940134201e-12</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0003655944019556046</v>
+        <v>9.038151086923629e-13</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0003385872114449739</v>
+        <v>3.841451896163806e-13</v>
       </c>
       <c r="DC6" t="n">
-        <v>7.347343489527702e-05</v>
+        <v>2.160935818305842e-13</v>
       </c>
       <c r="DD6" t="n">
-        <v>5.300988414091989e-05</v>
+        <v>4.2854275358363e-13</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0003579319454729557</v>
+        <v>5.817618522335755e-13</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0008135025855153799</v>
+        <v>6.729717911407862e-12</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0002078881370835006</v>
+        <v>5.46221965228022e-12</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0008379924693144858</v>
+        <v>8.427027521976105e-13</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.000978715717792511</v>
+        <v>3.692778288016951e-12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0002825289848260581</v>
+        <v>4.061691846572735e-13</v>
       </c>
       <c r="DK6" t="n">
-        <v>2.353233867324889e-05</v>
+        <v>5.312002465500398e-13</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0002615353441797197</v>
+        <v>8.609329612066507e-13</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0003964609350077808</v>
+        <v>1.141344939566136e-12</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.045045792125165e-06</v>
+        <v>1.680991066829729e-12</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.000199180212803185</v>
+        <v>2.0592590133095e-12</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0004630188923329115</v>
+        <v>7.512711698402785e-13</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0001436084567103535</v>
+        <v>2.531189233906384e-12</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0003760116815101355</v>
+        <v>2.087518959775769e-12</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0004390738904476166</v>
+        <v>1.799707843690157e-12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0002998476848006248</v>
+        <v>2.087400890159186e-14</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0002458750095684081</v>
+        <v>8.110529392188481e-13</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0001713598321657628</v>
+        <v>2.039610884699283e-12</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.000178265618160367</v>
+        <v>5.024049752611059e-13</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0004353183321654797</v>
+        <v>1.28086994136134e-12</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.10801177774556e-05</v>
+        <v>1.478409517204071e-12</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0002140381839126348</v>
+        <v>1.264127474573384e-12</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.000128076906548813</v>
+        <v>3.417524943594152e-12</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0001500280341133475</v>
+        <v>1.044017303164502e-12</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0001625186414457858</v>
+        <v>3.577068762722346e-12</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0006316484068520367</v>
+        <v>1.157097746611047e-12</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0001319856237387285</v>
+        <v>1.453737954668077e-12</v>
       </c>
       <c r="EF6" t="n">
-        <v>9.062456229003146e-05</v>
+        <v>4.85737426843269e-13</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.000841464614495635</v>
+        <v>3.784335583616183e-13</v>
       </c>
       <c r="EH6" t="n">
-        <v>8.780854113865644e-05</v>
+        <v>6.836947999931675e-13</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0001467073889216408</v>
+        <v>2.53583991912526e-13</v>
       </c>
       <c r="EJ6" t="n">
-        <v>5.231264731264673e-05</v>
+        <v>5.981142230798708e-14</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0002606102498248219</v>
+        <v>1.739618757205796e-12</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0003258554497733712</v>
+        <v>1.874971532200842e-12</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0002581375010777265</v>
+        <v>3.320001879750928e-13</v>
       </c>
       <c r="EN6" t="n">
-        <v>7.715347601333633e-05</v>
+        <v>1.043796017501097e-12</v>
       </c>
       <c r="EO6" t="n">
-        <v>9.837918332777917e-05</v>
+        <v>1.641104786787029e-12</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0005129871424287558</v>
+        <v>8.181117458830323e-13</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0003012271190527827</v>
+        <v>3.516783760905418e-13</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0001829946122597903</v>
+        <v>1.402285947950388e-13</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0001080279762391001</v>
+        <v>1.108583385679707e-12</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0003928482765331864</v>
+        <v>7.532653157910768e-14</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0002050250332104042</v>
+        <v>1.375860905240833e-12</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0003855999966617674</v>
+        <v>2.095573064034295e-12</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0005410747835412621</v>
+        <v>9.232957280669307e-13</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.000104258579085581</v>
+        <v>4.743438714732706e-13</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0007088562124408782</v>
+        <v>2.908299686146809e-13</v>
       </c>
       <c r="EZ6" t="n">
-        <v>8.531122148269787e-05</v>
+        <v>5.61122166526512e-13</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0003028867358807474</v>
+        <v>8.485215026270143e-13</v>
       </c>
       <c r="FB6" t="n">
-        <v>2.975588540721219e-05</v>
+        <v>1.612813073197106e-12</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0003933427215088159</v>
+        <v>1.126795596932684e-12</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0003495762648526579</v>
+        <v>6.610234820451921e-13</v>
       </c>
       <c r="FE6" t="n">
-        <v>6.293309706961736e-05</v>
+        <v>7.763158605539333e-13</v>
       </c>
       <c r="FF6" t="n">
-        <v>4.039522900711745e-05</v>
+        <v>6.133426557440591e-13</v>
       </c>
       <c r="FG6" t="n">
-        <v>5.788075213786215e-06</v>
+        <v>3.321624388302052e-13</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0002519759582355618</v>
+        <v>1.233801797707879e-12</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0004472840228118002</v>
+        <v>1.976869622860589e-12</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.00101405696477741</v>
+        <v>2.629173788404326e-12</v>
       </c>
       <c r="FK6" t="n">
-        <v>9.499092993792146e-05</v>
+        <v>3.397298067864263e-12</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0003116634325124323</v>
+        <v>1.929997828220564e-12</v>
       </c>
       <c r="FM6" t="n">
-        <v>2.97964179480914e-05</v>
+        <v>6.43207411160987e-14</v>
       </c>
       <c r="FN6" t="n">
-        <v>4.149097367189825e-05</v>
+        <v>1.403702024407871e-12</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0005382498493418097</v>
+        <v>4.442187936937181e-12</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.000528039294295013</v>
+        <v>4.917704264639777e-12</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.0009354888461530209</v>
+        <v>2.102049870972289e-12</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0001835601724451408</v>
+        <v>2.487261698685961e-13</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0005532417562790215</v>
+        <v>6.057078016236117e-12</v>
       </c>
       <c r="FT6" t="n">
-        <v>8.933589560911059e-05</v>
+        <v>6.763517697294663e-12</v>
       </c>
       <c r="FU6" t="n">
-        <v>3.51634735125117e-05</v>
+        <v>1.893581645651121e-12</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0002107370237354189</v>
+        <v>1.061115821945902e-12</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0006421430152840912</v>
+        <v>1.020396874634732e-11</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0001045713433995843</v>
+        <v>7.822551200548089e-14</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.0006659432547166944</v>
+        <v>1.911904662366126e-12</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0001275732065550983</v>
+        <v>1.566693281183917e-12</v>
       </c>
       <c r="GA6" t="n">
-        <v>2.023225897573866e-05</v>
+        <v>3.578378912627578e-12</v>
       </c>
       <c r="GB6" t="n">
-        <v>3.750919131562114e-05</v>
+        <v>2.136072351985319e-12</v>
       </c>
       <c r="GC6" t="n">
-        <v>8.582639566157013e-06</v>
+        <v>1.828498290279423e-13</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0001667873875703663</v>
+        <v>2.090382988234607e-12</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0007875175797380507</v>
+        <v>2.250983253959671e-12</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0004527908167801797</v>
+        <v>2.380276965113781e-12</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0003413668018765748</v>
+        <v>1.303345994498051e-13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.473968606864219e-06</v>
+        <v>2.594242687337101e-08</v>
       </c>
       <c r="B7" t="n">
-        <v>1.60379186127102e-05</v>
+        <v>9.199096950851526e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.617454245206318e-06</v>
+        <v>7.766914222884225e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>8.862977665557992e-06</v>
+        <v>6.153889131610413e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>4.74915987069835e-06</v>
+        <v>1.401801252853829e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.770798457480851e-06</v>
+        <v>5.586418794223391e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.566685850524664e-07</v>
+        <v>1.030262097856394e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.518821702324203e-07</v>
+        <v>2.516361874427275e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.963802323094569e-07</v>
+        <v>1.945983596485235e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>3.927023044525413e-06</v>
+        <v>1.374131031184334e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.288638668484055e-05</v>
+        <v>9.248969234931792e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>9.077858749151346e-07</v>
+        <v>1.549681982737638e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.841744496137835e-06</v>
+        <v>1.029064264912449e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.440377324499423e-06</v>
+        <v>5.141443892853204e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.49892353976611e-06</v>
+        <v>5.281913928456561e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.228272933280095e-06</v>
+        <v>6.71956579267885e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.277788209743449e-06</v>
+        <v>1.601539878492986e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.285629878111649e-07</v>
+        <v>5.015301063338029e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.529749624751275e-07</v>
+        <v>8.41157188347097e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.325604100406053e-06</v>
+        <v>1.424808004912848e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>4.21071234768533e-07</v>
+        <v>2.481271010879027e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.696159188213642e-06</v>
+        <v>4.211510029605847e-10</v>
       </c>
       <c r="W7" t="n">
-        <v>6.918968153968308e-08</v>
+        <v>2.674542898262189e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.665931904426543e-06</v>
+        <v>2.247876551564332e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.002929932132247e-06</v>
+        <v>3.076563359627471e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.098821596518974e-06</v>
+        <v>1.588072073843705e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.230214931842056e-06</v>
+        <v>6.836066823723286e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.101479700897471e-07</v>
+        <v>1.906189872613595e-09</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.948020210169489e-07</v>
+        <v>1.514693792614707e-08</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.650017106338055e-07</v>
+        <v>7.329537421441046e-09</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.926133788605512e-07</v>
+        <v>3.084394251118283e-08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.784094223467036e-07</v>
+        <v>1.72978005252844e-08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.275561061220287e-07</v>
+        <v>3.442326601543755e-08</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.148020474938676e-07</v>
+        <v>1.071889910164714e-09</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.19103617635119e-06</v>
+        <v>4.309208989639046e-08</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8.176878623089578e-07</v>
+        <v>2.532741794070148e-10</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.636162096474436e-06</v>
+        <v>8.954290642293472e-09</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.875494035630254e-06</v>
+        <v>1.427506646223264e-08</v>
       </c>
       <c r="AM7" t="n">
-        <v>6.685794460281613e-07</v>
+        <v>3.254031000210489e-08</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.454580621564673e-07</v>
+        <v>2.643634466892308e-08</v>
       </c>
       <c r="AO7" t="n">
-        <v>8.010966325855406e-07</v>
+        <v>2.593377601556313e-08</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.285637492605019e-07</v>
+        <v>2.300698476176422e-08</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.703636697442562e-07</v>
+        <v>2.020338119024245e-09</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.167076615933183e-07</v>
+        <v>7.029605786357251e-09</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.23807751606364e-06</v>
+        <v>3.85674869818331e-09</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.404030384350335e-07</v>
+        <v>3.367033762913252e-09</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.725540621730033e-06</v>
+        <v>7.133771617873208e-08</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.735145691687649e-07</v>
+        <v>4.831275646210997e-08</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.700117531479918e-06</v>
+        <v>5.343849807104561e-10</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.948364115378354e-06</v>
+        <v>9.092514829944776e-08</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.836600050519337e-07</v>
+        <v>5.943852698919727e-08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.132871716436057e-06</v>
+        <v>5.907171196639638e-09</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.287331982297474e-07</v>
+        <v>1.680266770165417e-08</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.149378360627452e-06</v>
+        <v>3.303268325538511e-09</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.508268042016425e-06</v>
+        <v>1.12662821294407e-08</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.163640258208034e-06</v>
+        <v>3.410535143189009e-08</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.532842922344571e-06</v>
+        <v>7.183452943593238e-09</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.661902827749145e-07</v>
+        <v>3.456082353636702e-08</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.512589046295034e-06</v>
+        <v>8.002004392437811e-08</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.056968696706463e-06</v>
+        <v>3.719180519112797e-09</v>
       </c>
       <c r="BI7" t="n">
-        <v>6.619936812057858e-07</v>
+        <v>1.087050716108706e-08</v>
       </c>
       <c r="BJ7" t="n">
-        <v>3.24725556311023e-06</v>
+        <v>4.080737170397697e-08</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.264159194164677e-07</v>
+        <v>1.116449332982938e-08</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.009026618703501e-06</v>
+        <v>8.844035725985577e-09</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.181253421440488e-06</v>
+        <v>1.811947214491738e-08</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.091235955958837e-06</v>
+        <v>1.949010730584178e-09</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.499587700796837e-07</v>
+        <v>1.243366565262249e-08</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.210435584653169e-06</v>
+        <v>3.920223790032651e-08</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.145866902646958e-07</v>
+        <v>1.15100518005562e-09</v>
       </c>
       <c r="BR7" t="n">
-        <v>8.395041959374794e-07</v>
+        <v>6.164239341188704e-09</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.828895955848566e-07</v>
+        <v>1.376922575957451e-08</v>
       </c>
       <c r="BT7" t="n">
-        <v>2.601594246698369e-07</v>
+        <v>7.271190316515685e-09</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.192300314618478e-07</v>
+        <v>3.365257406073852e-09</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.329377017915249e-06</v>
+        <v>2.597178117014209e-08</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.753739411469724e-06</v>
+        <v>2.741560223284978e-08</v>
       </c>
       <c r="BX7" t="n">
-        <v>2.314861376362387e-06</v>
+        <v>6.673185559691319e-09</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.801162726333132e-07</v>
+        <v>2.316750169484294e-08</v>
       </c>
       <c r="BZ7" t="n">
-        <v>7.935578878459637e-07</v>
+        <v>3.902631107166599e-08</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.849291948019527e-06</v>
+        <v>2.889084527168961e-08</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.70299858332146e-07</v>
+        <v>1.53230450550268e-09</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.490058593844878e-06</v>
+        <v>1.436585961300807e-09</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.461108922740095e-08</v>
+        <v>3.681598137461606e-09</v>
       </c>
       <c r="CE7" t="n">
-        <v>2.563821453804849e-06</v>
+        <v>3.08215248878696e-08</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.683616574155167e-06</v>
+        <v>5.191257979042518e-10</v>
       </c>
       <c r="CG7" t="n">
-        <v>8.471540127175103e-07</v>
+        <v>1.903820745496887e-08</v>
       </c>
       <c r="CH7" t="n">
-        <v>3.978788640779385e-07</v>
+        <v>8.2813995661013e-09</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.077976662600122e-06</v>
+        <v>9.350371144023484e-09</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.416346092104504e-07</v>
+        <v>8.328986389471993e-09</v>
       </c>
       <c r="CK7" t="n">
-        <v>2.882105718526873e-07</v>
+        <v>7.902782872548642e-10</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.387144720865763e-06</v>
+        <v>4.661961039431617e-09</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.680121269804658e-06</v>
+        <v>2.203896265484673e-08</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.529210973989393e-07</v>
+        <v>5.472053032917756e-08</v>
       </c>
       <c r="CO7" t="n">
-        <v>7.390124210360227e-07</v>
+        <v>4.442205536747679e-08</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.992484385482385e-06</v>
+        <v>2.991672332086637e-08</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.889996497084212e-06</v>
+        <v>2.191764103542937e-08</v>
       </c>
       <c r="CR7" t="n">
-        <v>5.347551450540777e-07</v>
+        <v>9.961492075660772e-09</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.00157967103587e-06</v>
+        <v>1.826900586365809e-08</v>
       </c>
       <c r="CT7" t="n">
-        <v>1.946629254234722e-06</v>
+        <v>2.187923087149102e-08</v>
       </c>
       <c r="CU7" t="n">
-        <v>5.041899839852704e-07</v>
+        <v>9.698957192938451e-10</v>
       </c>
       <c r="CV7" t="n">
-        <v>4.325052316289657e-08</v>
+        <v>7.196105489271076e-09</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.308157718289294e-06</v>
+        <v>2.894148920518091e-08</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.655009668866114e-06</v>
+        <v>2.726568526512096e-09</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.814695792745624e-06</v>
+        <v>2.349733563278278e-08</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.470023213798413e-07</v>
+        <v>1.297451568404995e-08</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.139839582720015e-06</v>
+        <v>1.177608766056437e-08</v>
       </c>
       <c r="DB7" t="n">
-        <v>4.731039666694414e-07</v>
+        <v>9.762747055219734e-09</v>
       </c>
       <c r="DC7" t="n">
-        <v>6.844252880000568e-07</v>
+        <v>3.669555104224287e-09</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.018647253658855e-06</v>
+        <v>5.44295586379917e-09</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.153488028649008e-06</v>
+        <v>2.218881256510485e-08</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.275940235245798e-06</v>
+        <v>6.174497357847031e-09</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.632446012285072e-06</v>
+        <v>1.055331644295165e-08</v>
       </c>
       <c r="DH7" t="n">
-        <v>7.14904081178247e-06</v>
+        <v>2.032903978488321e-08</v>
       </c>
       <c r="DI7" t="n">
-        <v>1.431511009286623e-06</v>
+        <v>4.170042089413073e-09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.172403585769644e-06</v>
+        <v>2.856849867782785e-08</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.162905836186837e-07</v>
+        <v>1.682668671065812e-09</v>
       </c>
       <c r="DL7" t="n">
-        <v>1.560949840495596e-06</v>
+        <v>3.82137237409097e-08</v>
       </c>
       <c r="DM7" t="n">
-        <v>3.438133830968582e-07</v>
+        <v>3.225622435820696e-08</v>
       </c>
       <c r="DN7" t="n">
-        <v>6.692298484267667e-07</v>
+        <v>1.694537843377475e-09</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.127834252656612e-06</v>
+        <v>1.525735093821368e-08</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.487938106947695e-06</v>
+        <v>3.567915962676693e-09</v>
       </c>
       <c r="DQ7" t="n">
-        <v>2.305656892076513e-07</v>
+        <v>2.014622246804265e-09</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.152327275936841e-08</v>
+        <v>5.299570116079622e-09</v>
       </c>
       <c r="DS7" t="n">
-        <v>1.072310965355427e-06</v>
+        <v>1.181387521143051e-08</v>
       </c>
       <c r="DT7" t="n">
-        <v>1.336472337243322e-07</v>
+        <v>2.174722624204151e-08</v>
       </c>
       <c r="DU7" t="n">
-        <v>5.138930418979726e-07</v>
+        <v>2.637819385142848e-08</v>
       </c>
       <c r="DV7" t="n">
-        <v>2.386621190453297e-06</v>
+        <v>2.811542998415462e-09</v>
       </c>
       <c r="DW7" t="n">
-        <v>4.710693133347377e-07</v>
+        <v>2.88740142906363e-09</v>
       </c>
       <c r="DX7" t="n">
-        <v>2.075582642646623e-06</v>
+        <v>5.576363815151808e-09</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.319155555596808e-06</v>
+        <v>2.099903184671348e-08</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.477321399714128e-07</v>
+        <v>2.395992382275836e-08</v>
       </c>
       <c r="EA7" t="n">
-        <v>9.683685675554443e-07</v>
+        <v>3.030178774565684e-08</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.11453766496561e-06</v>
+        <v>6.458169998779795e-09</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.434265411466185e-07</v>
+        <v>5.618451037747718e-09</v>
       </c>
       <c r="ED7" t="n">
-        <v>5.43406997621787e-07</v>
+        <v>3.97384098960174e-08</v>
       </c>
       <c r="EE7" t="n">
-        <v>5.190628939999442e-07</v>
+        <v>7.530410073286475e-09</v>
       </c>
       <c r="EF7" t="n">
-        <v>1.197243250317115e-06</v>
+        <v>1.012886485796116e-08</v>
       </c>
       <c r="EG7" t="n">
-        <v>1.879503997770371e-06</v>
+        <v>8.352887270746123e-09</v>
       </c>
       <c r="EH7" t="n">
-        <v>1.014123427012237e-06</v>
+        <v>1.270617033810595e-08</v>
       </c>
       <c r="EI7" t="n">
-        <v>6.995331887083012e-07</v>
+        <v>1.911567082402144e-08</v>
       </c>
       <c r="EJ7" t="n">
-        <v>3.89307558634755e-07</v>
+        <v>8.220010450088466e-09</v>
       </c>
       <c r="EK7" t="n">
-        <v>9.957029760698788e-07</v>
+        <v>9.987812354950165e-09</v>
       </c>
       <c r="EL7" t="n">
-        <v>3.646493951237062e-07</v>
+        <v>1.472776389732644e-08</v>
       </c>
       <c r="EM7" t="n">
-        <v>7.24413496300258e-07</v>
+        <v>8.579894572591229e-10</v>
       </c>
       <c r="EN7" t="n">
-        <v>6.898756623741065e-07</v>
+        <v>6.481006398217914e-09</v>
       </c>
       <c r="EO7" t="n">
-        <v>1.258603958831372e-07</v>
+        <v>4.938072173388264e-10</v>
       </c>
       <c r="EP7" t="n">
-        <v>3.747557855149353e-07</v>
+        <v>1.854373721243974e-08</v>
       </c>
       <c r="EQ7" t="n">
-        <v>1.981245304705226e-06</v>
+        <v>9.069149875529092e-09</v>
       </c>
       <c r="ER7" t="n">
-        <v>3.618654318415793e-07</v>
+        <v>5.925651080929129e-09</v>
       </c>
       <c r="ES7" t="n">
-        <v>8.946134357756819e-07</v>
+        <v>8.804008189144952e-09</v>
       </c>
       <c r="ET7" t="n">
-        <v>7.949710152388434e-07</v>
+        <v>5.127349655964508e-09</v>
       </c>
       <c r="EU7" t="n">
-        <v>1.229654458256846e-06</v>
+        <v>6.059190482687882e-09</v>
       </c>
       <c r="EV7" t="n">
-        <v>3.092486622335855e-06</v>
+        <v>1.522893988692431e-08</v>
       </c>
       <c r="EW7" t="n">
-        <v>4.956636416864058e-07</v>
+        <v>2.425452549914553e-08</v>
       </c>
       <c r="EX7" t="n">
-        <v>2.918382620009652e-07</v>
+        <v>4.221984983843186e-09</v>
       </c>
       <c r="EY7" t="n">
-        <v>2.225431444458081e-06</v>
+        <v>3.454215757869861e-08</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.416443865309702e-06</v>
+        <v>2.479182192871576e-09</v>
       </c>
       <c r="FA7" t="n">
-        <v>1.234450223819294e-06</v>
+        <v>2.372584972931691e-08</v>
       </c>
       <c r="FB7" t="n">
-        <v>2.044656355337793e-07</v>
+        <v>3.357673472592637e-09</v>
       </c>
       <c r="FC7" t="n">
-        <v>1.026642280521628e-06</v>
+        <v>7.834709769838355e-09</v>
       </c>
       <c r="FD7" t="n">
-        <v>7.284324397005548e-07</v>
+        <v>4.629384875443066e-09</v>
       </c>
       <c r="FE7" t="n">
-        <v>2.232308844440922e-07</v>
+        <v>5.593405738579804e-09</v>
       </c>
       <c r="FF7" t="n">
-        <v>1.446797114112996e-06</v>
+        <v>2.096017137631634e-09</v>
       </c>
       <c r="FG7" t="n">
-        <v>1.385362907058152e-06</v>
+        <v>5.72249359009902e-10</v>
       </c>
       <c r="FH7" t="n">
-        <v>5.388611512557873e-08</v>
+        <v>2.091288564542992e-08</v>
       </c>
       <c r="FI7" t="n">
-        <v>2.297442733834032e-06</v>
+        <v>5.640388600625101e-09</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.870413825599826e-06</v>
+        <v>1.514016645387528e-08</v>
       </c>
       <c r="FK7" t="n">
-        <v>8.475319646095159e-08</v>
+        <v>7.344569397105261e-09</v>
       </c>
       <c r="FL7" t="n">
-        <v>1.051657250172866e-06</v>
+        <v>3.401554149462527e-09</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.892810104209275e-07</v>
+        <v>2.267316334680913e-10</v>
       </c>
       <c r="FN7" t="n">
-        <v>2.483593561919406e-06</v>
+        <v>1.072323563278132e-08</v>
       </c>
       <c r="FO7" t="n">
-        <v>8.1107077676279e-07</v>
+        <v>3.257185454685896e-08</v>
       </c>
       <c r="FP7" t="n">
-        <v>6.875082476653915e-07</v>
+        <v>1.368991853212265e-08</v>
       </c>
       <c r="FQ7" t="n">
-        <v>9.372926683681726e-07</v>
+        <v>4.147866761172736e-08</v>
       </c>
       <c r="FR7" t="n">
-        <v>8.987927913040039e-07</v>
+        <v>2.890449479764357e-08</v>
       </c>
       <c r="FS7" t="n">
-        <v>2.776978362817317e-07</v>
+        <v>4.739619363647307e-09</v>
       </c>
       <c r="FT7" t="n">
-        <v>4.311190423322842e-06</v>
+        <v>4.888729421281823e-08</v>
       </c>
       <c r="FU7" t="n">
-        <v>6.210510719029116e-07</v>
+        <v>1.786239067769202e-08</v>
       </c>
       <c r="FV7" t="n">
-        <v>9.259276794182369e-07</v>
+        <v>2.363187512344211e-08</v>
       </c>
       <c r="FW7" t="n">
-        <v>1.408302864547295e-06</v>
+        <v>1.762430379415036e-08</v>
       </c>
       <c r="FX7" t="n">
-        <v>1.071268570740358e-06</v>
+        <v>4.173834167175983e-09</v>
       </c>
       <c r="FY7" t="n">
-        <v>2.904967914219014e-06</v>
+        <v>2.764302564628451e-09</v>
       </c>
       <c r="FZ7" t="n">
-        <v>1.450832087357412e-06</v>
+        <v>7.045859451437764e-09</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.629795320923222e-08</v>
+        <v>2.918827846087879e-08</v>
       </c>
       <c r="GB7" t="n">
-        <v>3.769535510400601e-07</v>
+        <v>1.225799017845475e-08</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.527874360363057e-06</v>
+        <v>1.689721607078809e-08</v>
       </c>
       <c r="GD7" t="n">
-        <v>1.741855271575332e-06</v>
+        <v>5.232680422295743e-08</v>
       </c>
       <c r="GE7" t="n">
-        <v>3.906287929567043e-06</v>
+        <v>2.767924733859672e-08</v>
       </c>
       <c r="GF7" t="n">
-        <v>5.338393975762301e-07</v>
+        <v>3.274329918312446e-09</v>
       </c>
       <c r="GG7" t="n">
-        <v>1.845956376200775e-06</v>
+        <v>9.61497881313278e-10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.009752591140568256</v>
+        <v>0.0008539468981325626</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1176171824336052</v>
+        <v>0.02375105023384094</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0110034141689539</v>
+        <v>0.0111073600128293</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03623878583312035</v>
+        <v>0.0148538751527667</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01331700012087822</v>
+        <v>0.001993428450077772</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0779438242316246</v>
+        <v>0.03950822725892067</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004343853332102299</v>
+        <v>0.006563236936926842</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03503170609474182</v>
+        <v>0.01069134101271629</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01571784727275372</v>
+        <v>0.004016980528831482</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01743549481034279</v>
+        <v>0.005434882827103138</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1105065867304802</v>
+        <v>0.02937126718461514</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001053359243087471</v>
+        <v>0.01223769783973694</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02984397113323212</v>
+        <v>0.01765193417668343</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002712178975343704</v>
+        <v>0.01302039436995983</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06758450716733932</v>
+        <v>0.04113378375768661</v>
       </c>
       <c r="P8" t="n">
-        <v>0.005171092227101326</v>
+        <v>0.00859562773257494</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009712258353829384</v>
+        <v>0.004514998756349087</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01734331622719765</v>
+        <v>0.001585301477462053</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001502708531916142</v>
+        <v>0.004537593107670546</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009227295406162739</v>
+        <v>0.000196693028556183</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0008289823308587074</v>
+        <v>0.004239867907017469</v>
       </c>
       <c r="V8" t="n">
-        <v>0.008766930550336838</v>
+        <v>0.00827092956751585</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01618906855583191</v>
+        <v>0.005959604401141405</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004489169921725988</v>
+        <v>0.009861204773187637</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003956917207688093</v>
+        <v>0.005182365886867046</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01912323758006096</v>
+        <v>0.003910947125405073</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0119464760646224</v>
+        <v>0.002640493912622333</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004908951930701733</v>
+        <v>0.001285254023969173</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.00693833502009511</v>
+        <v>0.0005206712521612644</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0008440574747510254</v>
+        <v>0.006576362065970898</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0006116093136370182</v>
+        <v>0.006715920753777027</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002297129947692156</v>
+        <v>0.005168015602976084</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.003318349830806255</v>
+        <v>0.008248033933341503</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0003777567762881517</v>
+        <v>0.004628267604857683</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.00436832569539547</v>
+        <v>0.01424108631908894</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001542880432680249</v>
+        <v>0.001061185146681964</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01330483332276344</v>
+        <v>0.006035151891410351</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.009425690397620201</v>
+        <v>0.004273816477507353</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.001346716657280922</v>
+        <v>0.004525227006524801</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.007174809463322163</v>
+        <v>0.006194085348397493</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.004900408908724785</v>
+        <v>0.0006113622803241014</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.01714728400111198</v>
+        <v>0.006014026701450348</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.005880817770957947</v>
+        <v>0.003705859882757068</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00747615797445178</v>
+        <v>0.004607828799635172</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.01204243954271078</v>
+        <v>0.006132674869149923</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.007405860815197229</v>
+        <v>0.00152528181206435</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.06347469240427017</v>
+        <v>0.0265369713306427</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.008691910654306412</v>
+        <v>0.01058410294353962</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.01066200248897076</v>
+        <v>0.002675733994692564</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.004946730099618435</v>
+        <v>0.01142083294689655</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.03921692073345184</v>
+        <v>0.02293825335800648</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.01810683868825436</v>
+        <v>0.0008394434116780758</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.01173321064561605</v>
+        <v>0.003290025051683187</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.01871565170586109</v>
+        <v>0.002301459200680256</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.004313353449106216</v>
+        <v>0.0009077431168407202</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0300352405756712</v>
+        <v>0.003445979673415422</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.02945238538086414</v>
+        <v>0.004490245599299669</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003645600285381079</v>
+        <v>0.005100582726299763</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.008094139397144318</v>
+        <v>0.007708976976573467</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.01542952749878168</v>
+        <v>0.002566609531641006</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.008727855980396271</v>
+        <v>0.007034856360405684</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.009197385050356388</v>
+        <v>0.01054235082119703</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.01549783162772655</v>
+        <v>0.004130682907998562</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.001923771458677948</v>
+        <v>0.0001098804641515017</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.02193686738610268</v>
+        <v>0.00907508097589016</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0135508356615901</v>
+        <v>0.0009341728873550892</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001501402352005243</v>
+        <v>0.001898029237054288</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01153931114822626</v>
+        <v>0.004198408685624599</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.005559909623116255</v>
+        <v>0.007616283372044563</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.006760413758456707</v>
+        <v>0.006721480283886194</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.005313540808856487</v>
+        <v>0.0005552226211875677</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.007902760058641434</v>
+        <v>0.004752444103360176</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002935685217380524</v>
+        <v>0.002504041651263833</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.04128904640674591</v>
+        <v>0.01386159751564264</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.006640354637056589</v>
+        <v>0.004807372111827135</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.004236573353409767</v>
+        <v>0.007171099074184895</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.005157436244189739</v>
+        <v>0.002306268783286214</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.01435357984155416</v>
+        <v>0.01914197020232677</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.00273628206923604</v>
+        <v>0.00631760386750102</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.002074369229376316</v>
+        <v>0.002520658075809479</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.01011229492723942</v>
+        <v>0.0003919512964785099</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.001900726230815053</v>
+        <v>9.981129551306367e-05</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.02006172016263008</v>
+        <v>0.007275840267539024</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.009212272241711617</v>
+        <v>0.001482305582612753</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0051932567730546</v>
+        <v>0.002212587045505643</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.004244493320584297</v>
+        <v>0.00142800051253289</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.01027830876410007</v>
+        <v>0.008680175058543682</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.007449094671756029</v>
+        <v>0.0005462087574414909</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.005443411879241467</v>
+        <v>0.003859847784042358</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.00930605735629797</v>
+        <v>0.00123861781321466</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.02745711430907249</v>
+        <v>0.0007413288694806397</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.009794063866138458</v>
+        <v>0.006922965869307518</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001503584790043533</v>
+        <v>0.00794672966003418</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0262581929564476</v>
+        <v>0.00184175802860409</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01126722246408463</v>
+        <v>0.002730711363255978</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.02835488505661488</v>
+        <v>0.001254526432603598</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.02128894254565239</v>
+        <v>0.005547894164919853</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.01902240887284279</v>
+        <v>0.005652383901178837</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.008041116409003735</v>
+        <v>0.0003239574143663049</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.001581819145940244</v>
+        <v>0.002412764355540276</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.01892919652163982</v>
+        <v>0.007019274868071079</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.009973875246942043</v>
+        <v>0.002687964355573058</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.01087765768170357</v>
+        <v>0.003080390393733978</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.003613083157688379</v>
+        <v>0.002171071944758296</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.009001761674880981</v>
+        <v>0.009599586948752403</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.007147864438593388</v>
+        <v>0.0008514861692674458</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.01118397153913975</v>
+        <v>0.003598126582801342</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.007215823046863079</v>
+        <v>0.001073221559636295</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.006881051231175661</v>
+        <v>0.0009776018559932709</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.02248879708349705</v>
+        <v>0.01342866010963917</v>
       </c>
       <c r="DG8" t="n">
-        <v>7.086006371537223e-05</v>
+        <v>0.001072397688403726</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.02278701588511467</v>
+        <v>0.003782819025218487</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.02556980587542057</v>
+        <v>0.003936929162591696</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.02277810499072075</v>
+        <v>0.007671205792576075</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.006859864108264446</v>
+        <v>0.002555804327130318</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.01430473383516073</v>
+        <v>0.01196588110178709</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.02399269118905067</v>
+        <v>0.003819471457973123</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.004759963601827621</v>
+        <v>0.002693830523639917</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.009959917515516281</v>
+        <v>0.005067912396043539</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.007831376977264881</v>
+        <v>0.002045369939878583</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.007048935629427433</v>
+        <v>0.005245470441877842</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.009458869695663452</v>
+        <v>0.00304070021957159</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0125341983512044</v>
+        <v>0.008095948025584221</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.01195274386554956</v>
+        <v>0.005402355454862118</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.007053056731820107</v>
+        <v>0.006056624930351973</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.002646478591486812</v>
+        <v>0.0009139036410488188</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.001928719924762845</v>
+        <v>0.002649895614013076</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.01462007407099009</v>
+        <v>0.0031288075260818</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.008744800463318825</v>
+        <v>0.01238044444471598</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.007680848240852356</v>
+        <v>0.001426951261237264</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.01313540432602167</v>
+        <v>0.006577631924301386</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.006981985177844763</v>
+        <v>0.003307748353108764</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.003901354735717177</v>
+        <v>0.0008943317225202918</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.005167911760509014</v>
+        <v>0.007466803770512342</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.01998599246144295</v>
+        <v>0.007119636982679367</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.01170893013477325</v>
+        <v>0.001143584493547678</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.02135079726576805</v>
+        <v>0.004960461053997278</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.01304016076028347</v>
+        <v>0.002077513374388218</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.002504467265680432</v>
+        <v>0.0005957985995337367</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.001019264338538051</v>
+        <v>0.00223105400800705</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0006030338117852807</v>
+        <v>0.004843077156692743</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.008207526989281178</v>
+        <v>0.0003689134900923818</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.003155686194077134</v>
+        <v>0.001603935612365603</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.004511358216404915</v>
+        <v>0.0002016729849856347</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0005672764964401722</v>
+        <v>0.001313419314101338</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.01001353375613689</v>
+        <v>0.006170746404677629</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.005244039930403233</v>
+        <v>0.004586353432387114</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.01167359668761492</v>
+        <v>0.0090270871296525</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.01441450044512749</v>
+        <v>0.005033165216445923</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.002256220206618309</v>
+        <v>0.002307637128978968</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0230617132037878</v>
+        <v>0.002916492288932204</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.02525861375033855</v>
+        <v>0.004902174696326256</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0004275057872291654</v>
+        <v>0.001884440425783396</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.003603959921747446</v>
+        <v>0.002207803539931774</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.01781005598604679</v>
+        <v>0.008282555267214775</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.007391038816422224</v>
+        <v>0.00223114900290966</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.00443979911506176</v>
+        <v>0.003325199708342552</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.002870753174647689</v>
+        <v>4.430045373737812e-05</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.008202780969440937</v>
+        <v>0.008502994664013386</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.01205866411328316</v>
+        <v>0.0006375545635819435</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.008826788514852524</v>
+        <v>0.003300932701677084</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.01110531855374575</v>
+        <v>0.0004338832513894886</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.005216150544583797</v>
+        <v>0.002754225861281157</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.006327069830149412</v>
+        <v>0.007888717576861382</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.00941268727183342</v>
+        <v>0.007267401553690434</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.01571594551205635</v>
+        <v>0.001776613760739565</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.006304016802459955</v>
+        <v>0.0006293234182521701</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.00499290507286787</v>
+        <v>0.007518633268773556</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.007213637232780457</v>
+        <v>0.001935959211550653</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.005134713370352983</v>
+        <v>0.003897653892636299</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.004970669746398926</v>
+        <v>0.007040023803710938</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.01211411692202091</v>
+        <v>0.007518532685935497</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.01011715549975634</v>
+        <v>0.01399617269635201</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.02223602496087551</v>
+        <v>0.002038692124187946</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.007285996805876493</v>
+        <v>0.003590642940253019</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.005712189245969057</v>
+        <v>0.005004416219890118</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.01269803754985332</v>
+        <v>0.003217518096789718</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.004455702379345894</v>
+        <v>0.0009420185815542936</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.005428890697658062</v>
+        <v>0.0127255329862237</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.00981968455016613</v>
+        <v>0.003623921424150467</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0158682856708765</v>
+        <v>0.003088912460952997</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01040805131196976</v>
+        <v>0.003812986426055431</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.007774246390908957</v>
+        <v>0.008870966732501984</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.003830933710560203</v>
+        <v>0.002647125627845526</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.003310920437797904</v>
+        <v>0.01353198289871216</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.007393564097583294</v>
+        <v>0.01207139529287815</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.02208296395838261</v>
+        <v>0.001268247375264764</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0003983583301305771</v>
+        <v>0.002279257867485285</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.00472016166895628</v>
+        <v>0.0004152805777266622</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.00013454828877002</v>
+        <v>3.903908236679854e-06</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02434697560966015</v>
+        <v>2.394025432295166e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.093230093829334e-05</v>
+        <v>1.014966801449191e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008154284209012985</v>
+        <v>2.219171619799454e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01011898647993803</v>
+        <v>1.29307863971917e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01631893031299114</v>
+        <v>3.243148239562288e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009253626340068877</v>
+        <v>4.608184099197388e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005942605435848236</v>
+        <v>8.242839612648822e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002425724640488625</v>
+        <v>1.464340471102332e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002153058303520083</v>
+        <v>1.099876612897788e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02604266442358494</v>
+        <v>2.878342638723552e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002483113901689649</v>
+        <v>1.747696842357982e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005814370699226856</v>
+        <v>1.132904617406894e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005319612100720406</v>
+        <v>1.291290209337603e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01493924763053656</v>
+        <v>3.742420449270867e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001194590586237609</v>
+        <v>6.780638841519249e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003501332830637693</v>
+        <v>5.772067197540309e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001069237478077412</v>
+        <v>2.577532995928777e-06</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00103890779428184</v>
+        <v>1.162376520369435e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002662984654307365</v>
+        <v>3.182844011462294e-06</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001098539214581251</v>
+        <v>5.123987193655921e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002824567025527358</v>
+        <v>2.80534572993929e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001996297854930162</v>
+        <v>5.301386408973485e-06</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001218332559801638</v>
+        <v>5.606606009678217e-06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002224474737886339</v>
+        <v>5.070930910733296e-06</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001560331089422107</v>
+        <v>5.485421752382535e-06</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001909558312036097</v>
+        <v>5.437335403257748e-06</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001266015460714698</v>
+        <v>6.619731721002609e-06</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.00157278694678098</v>
+        <v>6.23167579760775e-08</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.003136139130219817</v>
+        <v>1.862592398538254e-06</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001421782188117504</v>
+        <v>7.111972536222311e-06</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.9391327239573e-05</v>
+        <v>4.239999725541566e-06</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0003825474996119738</v>
+        <v>9.04866919881897e-06</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001973935402929783</v>
+        <v>7.268374133673206e-07</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.003464783309027553</v>
+        <v>1.561389944981784e-05</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.001571971690282226</v>
+        <v>3.446489017733256e-06</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.002527779433876276</v>
+        <v>3.391610789549304e-06</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.004252198152244091</v>
+        <v>2.360752205277095e-06</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.00260465731844306</v>
+        <v>1.704453893580649e-06</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.001345210941508412</v>
+        <v>1.176823388959747e-06</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0002360313083045185</v>
+        <v>1.45421427077963e-06</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001596729969605803</v>
+        <v>2.200520839323872e-06</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.504704752936959e-05</v>
+        <v>3.203403821316897e-06</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.001545802457258105</v>
+        <v>6.556971584359417e-06</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001348117832094431</v>
+        <v>1.582523736942676e-06</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001966215204447508</v>
+        <v>2.984892489621416e-06</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01578503474593163</v>
+        <v>2.743442200880963e-05</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.003806422231718898</v>
+        <v>6.407896307791816e-06</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001321960822679102</v>
+        <v>3.256082663938287e-06</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001074899802915752</v>
+        <v>9.639974450692534e-06</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.008002392947673798</v>
+        <v>2.034947101492435e-05</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.81737728882581e-05</v>
+        <v>1.378142314933939e-06</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.001456849742680788</v>
+        <v>3.267008423790685e-06</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.168307689018548e-05</v>
+        <v>1.205659373226808e-06</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001311324769631028</v>
+        <v>3.203883352398407e-06</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.005925057455897331</v>
+        <v>4.593143785314169e-07</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.004181070253252983</v>
+        <v>6.589997610717546e-06</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002240726258605719</v>
+        <v>1.668212007643888e-06</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.008191689848899841</v>
+        <v>3.898003342328593e-06</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.007506339810788631</v>
+        <v>2.505631073290715e-06</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0004484452656470239</v>
+        <v>9.349093943455955e-08</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.000896957702934742</v>
+        <v>1.171186340798158e-05</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0005387975834310055</v>
+        <v>5.166260962141678e-06</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.002773253712803125</v>
+        <v>9.110719929594779e-07</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.003718063002452254</v>
+        <v>9.772707926458679e-06</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.001187262940220535</v>
+        <v>5.17816852152464e-06</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0004341613675933331</v>
+        <v>2.907552925535128e-06</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0001487643894506618</v>
+        <v>4.603282377502182e-06</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0005400781519711018</v>
+        <v>7.30281999494764e-06</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.001905255019664764</v>
+        <v>9.097507245314773e-06</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.001348446472547948</v>
+        <v>1.27583086850791e-06</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0006826428580097854</v>
+        <v>7.873601134633645e-06</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0008548377663828433</v>
+        <v>1.024299535856699e-06</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.00995596032589674</v>
+        <v>1.431986584066181e-05</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0008319583721458912</v>
+        <v>3.453586714385892e-06</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001572168665006757</v>
+        <v>4.050158622703748e-06</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0001461422070860863</v>
+        <v>7.749949872959405e-07</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.00195536739192903</v>
+        <v>1.238495406141737e-05</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001570007880218327</v>
+        <v>3.703130005305866e-06</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0002329292619833723</v>
+        <v>1.618693659111159e-06</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.001588587299920619</v>
+        <v>2.015463564930542e-07</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0002088951296173036</v>
+        <v>6.087730071158148e-07</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.004138019401580095</v>
+        <v>6.624774869123939e-06</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0006702932878397405</v>
+        <v>2.785440756269963e-06</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001712844823487103</v>
+        <v>1.437996274944453e-06</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0001103139657061547</v>
+        <v>7.419614576065214e-07</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002584339817985892</v>
+        <v>7.76870729168877e-06</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.001741227810271084</v>
+        <v>1.13769169729494e-06</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0005872623296454549</v>
+        <v>1.851223260018742e-06</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0005152971716597676</v>
+        <v>2.722085810091812e-06</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.004764007404446602</v>
+        <v>8.890538083505817e-08</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.003160039428621531</v>
+        <v>7.988960533111822e-06</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0006030828808434308</v>
+        <v>7.805561835994013e-06</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.002847537398338318</v>
+        <v>8.395051736442838e-06</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001213580835610628</v>
+        <v>8.469867793792218e-07</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0007862760685384274</v>
+        <v>2.103664201058564e-06</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.004991925321519375</v>
+        <v>1.649046907914453e-07</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.004487641621381044</v>
+        <v>1.181181232823292e-05</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.002069565933197737</v>
+        <v>7.770596539558028e-07</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.95388454105705e-05</v>
+        <v>1.064719185706053e-06</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.003519168123602867</v>
+        <v>5.896113179915119e-06</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0005628271028399467</v>
+        <v>3.235039912397042e-06</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.00241574365645647</v>
+        <v>3.276186589573626e-06</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0005192665266804397</v>
+        <v>2.301703716511838e-07</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.002766334917396307</v>
+        <v>8.880101631802972e-06</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001599437324330211</v>
+        <v>2.188738790209754e-08</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0004720619763247669</v>
+        <v>1.738091896186233e-06</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0001411699195159599</v>
+        <v>2.213974312326172e-06</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.001294292276725173</v>
+        <v>3.038531986021553e-07</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.003563900478184223</v>
+        <v>1.274853821087163e-05</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0008129904745146632</v>
+        <v>1.338341917289654e-06</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.004932497162371874</v>
+        <v>4.467626240511891e-06</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.006409991532564163</v>
+        <v>5.833320756210014e-06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001471528201363981</v>
+        <v>1.084471023204969e-05</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0006731032044626772</v>
+        <v>5.264277660899097e-06</v>
       </c>
       <c r="DL9" t="n">
-        <v>3.179244231432676e-05</v>
+        <v>8.546789104002528e-06</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.003026108257472515</v>
+        <v>9.33834417082835e-06</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0001080713118426502</v>
+        <v>7.03284229075507e-07</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0003559901379048824</v>
+        <v>1.038459117808088e-06</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.002016432350501418</v>
+        <v>1.235123818332795e-06</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.001744127366691828</v>
+        <v>2.959096946142381e-06</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0006784264696761966</v>
+        <v>7.775289304845501e-06</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.001241126796230674</v>
+        <v>1.392803028466005e-07</v>
       </c>
       <c r="DT9" t="n">
-        <v>7.591821486130357e-05</v>
+        <v>5.230923306953628e-06</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0008827490964904428</v>
+        <v>4.593392986862455e-06</v>
       </c>
       <c r="DV9" t="n">
-        <v>9.605864761397243e-05</v>
+        <v>2.240591584268259e-06</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0004870875854976475</v>
+        <v>1.061164766724687e-06</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.002225231612101197</v>
+        <v>1.935693489940604e-06</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0008850935846567154</v>
+        <v>4.473806257010438e-06</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.001493937685154378</v>
+        <v>3.419871063670143e-06</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001440113526768982</v>
+        <v>3.815710897470126e-06</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0009206769755110145</v>
+        <v>1.221506749971013e-06</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.001200830796733499</v>
+        <v>1.153998141489865e-06</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001885435311123729</v>
+        <v>7.178467512858333e-06</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.001129788113757968</v>
+        <v>9.789953764993697e-06</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0004582517431117594</v>
+        <v>1.808532488212222e-06</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.004748517647385597</v>
+        <v>4.347360118117649e-06</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.000320409337291494</v>
+        <v>7.128212473617168e-07</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0002371369191678241</v>
+        <v>2.241727543150773e-06</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0004483902885112911</v>
+        <v>1.278273657590034e-06</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.002622783416882157</v>
+        <v>2.361153519814252e-06</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.001073385355994105</v>
+        <v>1.052479319696431e-06</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.001889965613372624</v>
+        <v>2.293320676471922e-06</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0005819345824420452</v>
+        <v>2.671937124887336e-07</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0004274732200428843</v>
+        <v>3.463004759396426e-06</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.002036465331912041</v>
+        <v>7.714108505751938e-06</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0009308990556746721</v>
+        <v>4.04633283324074e-06</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.001485048327594995</v>
+        <v>7.1613681029703e-07</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0002288562245666981</v>
+        <v>2.482887566657155e-06</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.002571301069110632</v>
+        <v>6.886340543132974e-06</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002293385565280914</v>
+        <v>2.406038447588799e-06</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.003460174659267068</v>
+        <v>1.108280571315845e-06</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0003312714397907257</v>
+        <v>1.227899701916613e-06</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0002726621751207858</v>
+        <v>1.19499259199074e-06</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.00358064635656774</v>
+        <v>8.19875185698038e-06</v>
       </c>
       <c r="EZ9" t="n">
-        <v>1.405959483236074e-05</v>
+        <v>2.205712689828943e-06</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.001524672959931195</v>
+        <v>3.587660330595099e-06</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0008418317884206772</v>
+        <v>2.104560280713486e-06</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.002916100900620222</v>
+        <v>7.467395789717557e-06</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.001928590820170939</v>
+        <v>1.616185500097345e-06</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0001765429769875482</v>
+        <v>1.184183815894357e-06</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0007732697413302958</v>
+        <v>2.304714712408895e-07</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.00027720961952582</v>
+        <v>3.518985067785252e-07</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0007889402331784368</v>
+        <v>8.162618541973643e-06</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0007904605008661747</v>
+        <v>2.945548430943745e-06</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.003204884007573128</v>
+        <v>4.674997398979031e-06</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.001716805156320333</v>
+        <v>4.315227670304012e-06</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0002033742202911526</v>
+        <v>1.296161462960299e-05</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0001355433487333357</v>
+        <v>2.501796188880689e-06</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0004227758035995066</v>
+        <v>4.547689059108961e-06</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001275183749385178</v>
+        <v>1.189481554320082e-05</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.001263735932298005</v>
+        <v>3.800155127464677e-06</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.00466736126691103</v>
+        <v>6.668276000709739e-06</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.001062831142917275</v>
+        <v>6.633333214267623e-06</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.001292412169277668</v>
+        <v>1.495244305260712e-06</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.003612762782722712</v>
+        <v>7.133154213079251e-06</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.000292343640467152</v>
+        <v>9.435439096705522e-08</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.001063860487192869</v>
+        <v>7.333620715144207e-07</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.002497198758646846</v>
+        <v>1.850242915679701e-05</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0007776624988764524</v>
+        <v>1.052068910212256e-06</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.003495440352708101</v>
+        <v>4.086507033207454e-06</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0001804899075068533</v>
+        <v>2.826825493684737e-06</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0007767427014186978</v>
+        <v>8.354762030648999e-06</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0004353890544734895</v>
+        <v>3.676813548736391e-06</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.001622195006348193</v>
+        <v>1.543082362331916e-05</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.002576781203970313</v>
+        <v>7.113662377378205e-06</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.005157682579010725</v>
+        <v>2.565260047049378e-06</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.00158224138431251</v>
+        <v>4.32445040132734e-06</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.001506511238403618</v>
+        <v>2.413185939076357e-06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0003225596155971289</v>
+        <v>0.06372648477554321</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1102806031703949</v>
+        <v>0.4817065894603729</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002540800953283906</v>
+        <v>0.1967755854129791</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07739337533712387</v>
+        <v>0.3466974496841431</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01997094042599201</v>
+        <v>0.1512134075164795</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02415628544986248</v>
+        <v>0.4644452333450317</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01355324126780033</v>
+        <v>0.1942046731710434</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01266923919320107</v>
+        <v>0.1481205523014069</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03664301708340645</v>
+        <v>0.0004634857177734375</v>
       </c>
       <c r="J10" t="n">
-        <v>0.008693627081811428</v>
+        <v>0.05281800031661987</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09899814426898956</v>
+        <v>0.4949536621570587</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0160228069871664</v>
+        <v>0.2965412735939026</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07104150950908661</v>
+        <v>0.5208014249801636</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02505199797451496</v>
+        <v>0.2504059672355652</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02014086022973061</v>
+        <v>0.4122695028781891</v>
       </c>
       <c r="P10" t="n">
-        <v>0.007861165329813957</v>
+        <v>0.1549289375543594</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01150821428745985</v>
+        <v>0.08560182154178619</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0367414802312851</v>
+        <v>0.02046503499150276</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01712483540177345</v>
+        <v>0.04494922980666161</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01664794981479645</v>
+        <v>0.005185829941183329</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003329872619360685</v>
+        <v>0.01652591302990913</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01559127401560545</v>
+        <v>0.04256221279501915</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02873981185257435</v>
+        <v>0.01717341877520084</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02187981456518173</v>
+        <v>0.1741334199905396</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.005592147819697857</v>
+        <v>0.006217051297426224</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01413921546190977</v>
+        <v>0.0357227623462677</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.008360534906387329</v>
+        <v>0.02564658597111702</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.006262824870646</v>
+        <v>0.07819803059101105</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.009026008658111095</v>
+        <v>0.03540686517953873</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0003763313870877028</v>
+        <v>0.03917790204286575</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.002163509838283062</v>
+        <v>0.07879155874252319</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.008280055597424507</v>
+        <v>0.01594237983226776</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003109314013272524</v>
+        <v>0.3092209100723267</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0005461545661091805</v>
+        <v>0.009059436619281769</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0248815082013607</v>
+        <v>0.183954045176506</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.02484064549207687</v>
+        <v>0.04812954366207123</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0001039892667904496</v>
+        <v>0.03955024480819702</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01278728153556585</v>
+        <v>0.2288150191307068</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.003451685886830091</v>
+        <v>0.004131361842155457</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.002779733389616013</v>
+        <v>0.02999100461602211</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.01749135181307793</v>
+        <v>0.1704323887825012</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.002004248090088367</v>
+        <v>0.01973569020628929</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.009876063093543053</v>
+        <v>0.03494862839579582</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.01468356978148222</v>
+        <v>0.04297564551234245</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.005827759858220816</v>
+        <v>0.03469440340995789</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.01117242127656937</v>
+        <v>0.02295781672000885</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.06280295550823212</v>
+        <v>0.3417682945728302</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.005130819976329803</v>
+        <v>0.08072155714035034</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.03693301975727081</v>
+        <v>0.1631509065628052</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0345785841345787</v>
+        <v>0.2139683067798615</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.01138612255454063</v>
+        <v>0.2283539772033691</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.003460139036178589</v>
+        <v>0.02516576647758484</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.005889724940061569</v>
+        <v>0.0439894013106823</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.02227377519011497</v>
+        <v>0.08932764828205109</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.01224813610315323</v>
+        <v>0.06437468528747559</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02509380877017975</v>
+        <v>0.05514738708734512</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.006573008839040995</v>
+        <v>0.2200226187705994</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.004896689206361771</v>
+        <v>0.01337278261780739</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.01463914103806019</v>
+        <v>0.01061015203595161</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.00878865085542202</v>
+        <v>0.1355712711811066</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.006453053094446659</v>
+        <v>0.04289386793971062</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01784418150782585</v>
+        <v>0.02731084451079369</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.003247631248086691</v>
+        <v>0.0811002105474472</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.006390747614204884</v>
+        <v>0.01478997059166431</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.01604835130274296</v>
+        <v>0.03285300731658936</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.00543610192835331</v>
+        <v>0.02673318423330784</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.009317565709352493</v>
+        <v>0.05771315842866898</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02162119187414646</v>
+        <v>0.002926317043602467</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.004184882156550884</v>
+        <v>0.06147123873233795</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.006962435785681009</v>
+        <v>0.02350175008177757</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.002761074109002948</v>
+        <v>0.04939056187868118</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.007075971458107233</v>
+        <v>0.01230732537806034</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.01567754335701466</v>
+        <v>0.03127060830593109</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.04389910399913788</v>
+        <v>0.2847917973995209</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.004058717284351587</v>
+        <v>0.07449027895927429</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.02539185062050819</v>
+        <v>0.197539895772934</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.005071807187050581</v>
+        <v>0.01049159839749336</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.00640933308750391</v>
+        <v>0.1859531998634338</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0115591436624527</v>
+        <v>0.01165299490094185</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.009758559055626392</v>
+        <v>0.02674302272498608</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.01657422631978989</v>
+        <v>0.01645991019904613</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.005941148847341537</v>
+        <v>0.01995249837636948</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.01273254863917828</v>
+        <v>0.151510626077652</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.005234104581177235</v>
+        <v>0.05261341482400894</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01413883827626705</v>
+        <v>0.1123168095946312</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.003723234869539738</v>
+        <v>0.0005264659412205219</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.004473356995731592</v>
+        <v>0.1025502234697342</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.007624505087733269</v>
+        <v>0.003130368888378143</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0004423577920533717</v>
+        <v>0.06656947731971741</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.002431873697787523</v>
+        <v>0.02375933900475502</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.02261845953762531</v>
+        <v>0.05231167748570442</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.001964013325050473</v>
+        <v>0.04967062175273895</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0007619219832122326</v>
+        <v>0.2346514165401459</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0128937903791666</v>
+        <v>0.153374046087265</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.007738944608718157</v>
+        <v>0.01008325070142746</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.002940029604360461</v>
+        <v>0.03988058865070343</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.02254264988005161</v>
+        <v>0.105716660618782</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.03758225589990616</v>
+        <v>0.009438950568437576</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.003241162514314055</v>
+        <v>0.009048726409673691</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.006570430472493172</v>
+        <v>0.006340617313981056</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.01255148835480213</v>
+        <v>0.1301508396863937</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.00505510251969099</v>
+        <v>0.065179243683815</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01639693416655064</v>
+        <v>0.1208849549293518</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.00279956916347146</v>
+        <v>0.05684109032154083</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.006871540099382401</v>
+        <v>0.1088386327028275</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.009461104869842529</v>
+        <v>0.00477182911708951</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.002777246758341789</v>
+        <v>0.06864017993211746</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.006081304512917995</v>
+        <v>0.003073347266763449</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0133975176140666</v>
+        <v>0.07863291352987289</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.01853220909833908</v>
+        <v>0.1087391600012779</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.003095035906881094</v>
+        <v>0.006257221102714539</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.02976882457733154</v>
+        <v>0.1534194350242615</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.005618868861347437</v>
+        <v>0.0124695748090744</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.00945111270993948</v>
+        <v>0.3710533678531647</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0147403422743082</v>
+        <v>0.01536274142563343</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.002078147605061531</v>
+        <v>0.2379107177257538</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0009610871784389019</v>
+        <v>0.00673653744161129</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.01439638994634151</v>
+        <v>0.007183795794844627</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.005278841592371464</v>
+        <v>0.1322162598371506</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.003797041019424796</v>
+        <v>0.01498418301343918</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.003090411890298128</v>
+        <v>0.03741063922643661</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.002358583733439445</v>
+        <v>0.01989606395363808</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.01743292436003685</v>
+        <v>0.002215631306171417</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.005871916189789772</v>
+        <v>0.02207704074680805</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.00346813490614295</v>
+        <v>0.105796754360199</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0007323684985749424</v>
+        <v>0.1298048198223114</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.01111135352402925</v>
+        <v>0.009404504671692848</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.01614691503345966</v>
+        <v>0.05204978212714195</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.001028102589771152</v>
+        <v>0.1544942557811737</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.007357004564255476</v>
+        <v>0.04720991104841232</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.002681851619854569</v>
+        <v>0.09228523075580597</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.004471894353628159</v>
+        <v>0.1515118926763535</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.004690642468631268</v>
+        <v>0.04776839166879654</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.004709634464234114</v>
+        <v>0.1940712779760361</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.01923193782567978</v>
+        <v>0.2202415466308594</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.003814245807006955</v>
+        <v>0.03053133934736252</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.006716744974255562</v>
+        <v>0.06920696794986725</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.003475601552054286</v>
+        <v>0.07697796821594238</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.01016984693706036</v>
+        <v>0.08120451867580414</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.005299518350511789</v>
+        <v>0.07030939310789108</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.00758060859516263</v>
+        <v>0.08287394046783447</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.003032964887097478</v>
+        <v>0.003454529214650393</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.005573092959821224</v>
+        <v>0.02035056799650192</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.001457392238080502</v>
+        <v>0.02044573612511158</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.00951731950044632</v>
+        <v>0.001711102202534676</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.01262808032333851</v>
+        <v>0.1138415634632111</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.003794170450419188</v>
+        <v>0.05664375796914101</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0118335485458374</v>
+        <v>0.09411860257387161</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0152529701590538</v>
+        <v>0.02409739978611469</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.02879751101136208</v>
+        <v>0.02508640289306641</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01096358243376017</v>
+        <v>0.05671545118093491</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.002462036674842238</v>
+        <v>0.07609909772872925</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.006148446816951036</v>
+        <v>0.04525093734264374</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.00642464542761445</v>
+        <v>0.004704286810010672</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.01378188189119101</v>
+        <v>0.162556990981102</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.002844619797542691</v>
+        <v>0.03378616273403168</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01652162149548531</v>
+        <v>0.1370651125907898</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0009351181797683239</v>
+        <v>0.02571955882012844</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.006443202495574951</v>
+        <v>0.1154664680361748</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.009009476751089096</v>
+        <v>0.002230593003332615</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001074720756150782</v>
+        <v>0.0615091361105442</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.003233850467950106</v>
+        <v>0.01550780422985554</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.002939324593171477</v>
+        <v>0.01517466828227043</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0004153936170041561</v>
+        <v>0.02793799713253975</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.003925295546650887</v>
+        <v>0.04919131100177765</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.008660050109028816</v>
+        <v>0.08716446161270142</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01090301107615232</v>
+        <v>0.0432361364364624</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.002592784818261862</v>
+        <v>0.1336171925067902</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.008572820574045181</v>
+        <v>0.01434663403779268</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.007128340657800436</v>
+        <v>0.1003976389765739</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0141217727214098</v>
+        <v>0.03219571337103844</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.004434868227690458</v>
+        <v>0.1020393520593643</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.01863945461809635</v>
+        <v>0.07069317996501923</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.009976654313504696</v>
+        <v>0.1527975797653198</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01458568591624498</v>
+        <v>0.07266020774841309</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.004165517631918192</v>
+        <v>0.1717156022787094</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.003648602170869708</v>
+        <v>0.1594795137643814</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0114800501614809</v>
+        <v>0.0532575435936451</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01099793147295713</v>
+        <v>0.1488576382398605</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.004646915476769209</v>
+        <v>0.01770923659205437</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001037499052472413</v>
+        <v>0.02152890339493752</v>
       </c>
       <c r="FZ10" t="n">
-        <v>1.523667015135288e-05</v>
+        <v>0.08009668439626694</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.002615128410980105</v>
+        <v>0.0883467048406601</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.006235203705728054</v>
+        <v>0.08264753967523575</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.02883143909275532</v>
+        <v>0.2278951406478882</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.005909739062190056</v>
+        <v>0.1308386623859406</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.03210699930787086</v>
+        <v>0.09021274000406265</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.002370820613577962</v>
+        <v>0.05753991007804871</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.005527293309569359</v>
+        <v>0.02688394114375114</v>
       </c>
     </row>
     <row r="11">
@@ -6689,1140 +6689,1140 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.937104288022965e-05</v>
+        <v>0.006291714496910572</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001247704494744539</v>
+        <v>0.03039777651429176</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001756073907017708</v>
+        <v>0.008228731341660023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0002757367619778961</v>
+        <v>0.002692782320082188</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0004606297588907182</v>
+        <v>0.001421818509697914</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0002125478495145217</v>
+        <v>0.02131581492722034</v>
       </c>
       <c r="G12" t="n">
-        <v>8.315850573126227e-05</v>
+        <v>0.006195808295160532</v>
       </c>
       <c r="H12" t="n">
-        <v>2.003303052333649e-05</v>
+        <v>0.02361500635743141</v>
       </c>
       <c r="I12" t="n">
-        <v>7.359907613135874e-05</v>
+        <v>0.006002416834235191</v>
       </c>
       <c r="J12" t="n">
-        <v>2.081922139041126e-05</v>
+        <v>0.004290665034204721</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0009366983431391418</v>
+        <v>0.05061623081564903</v>
       </c>
       <c r="L12" t="n">
-        <v>3.273133188486099e-05</v>
+        <v>0.009994943626224995</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0001635908265598118</v>
+        <v>0.01257813721895218</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0003144193615298718</v>
+        <v>0.003663116134703159</v>
       </c>
       <c r="O12" t="n">
-        <v>8.856844942783937e-05</v>
+        <v>0.01528834458440542</v>
       </c>
       <c r="P12" t="n">
-        <v>5.401160888141021e-05</v>
+        <v>0.009117045439779758</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0002334368327865377</v>
+        <v>0.002061341423541307</v>
       </c>
       <c r="R12" t="n">
-        <v>6.709951412631199e-05</v>
+        <v>0.01393012888729572</v>
       </c>
       <c r="S12" t="n">
-        <v>2.253132879559416e-05</v>
+        <v>0.005871362518519163</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0001909808488562703</v>
+        <v>0.01035651750862598</v>
       </c>
       <c r="U12" t="n">
-        <v>9.317754302173853e-05</v>
+        <v>0.002993379486724734</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0001339534937869757</v>
+        <v>0.002051955787464976</v>
       </c>
       <c r="W12" t="n">
-        <v>5.424235132522881e-05</v>
+        <v>0.00338219478726387</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0001653577928664163</v>
+        <v>0.00647221552208066</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.330717506993096e-05</v>
+        <v>0.003058810951188207</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0001174316930701025</v>
+        <v>0.006725167389959097</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.502015847014263e-05</v>
+        <v>0.003976072650402784</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.285654434468597e-05</v>
+        <v>0.008125597611069679</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.000204124822630547</v>
+        <v>0.004524078220129013</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.253957088920288e-05</v>
+        <v>1.717248233035207e-05</v>
       </c>
       <c r="AE12" t="n">
-        <v>6.133116403361782e-05</v>
+        <v>0.01789359748363495</v>
       </c>
       <c r="AF12" t="n">
-        <v>6.361072883009911e-05</v>
+        <v>0.02327987551689148</v>
       </c>
       <c r="AG12" t="n">
-        <v>8.947710739448667e-05</v>
+        <v>0.002253787126392126</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.094200580264442e-05</v>
+        <v>0.0008497727103531361</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.685547876055352e-06</v>
+        <v>0.01113931555300951</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.524756928323768e-05</v>
+        <v>0.004058266989886761</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0001658812252571806</v>
+        <v>0.0003814898664131761</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0001547122228657827</v>
+        <v>0.00473338458687067</v>
       </c>
       <c r="AM12" t="n">
-        <v>5.600177610176615e-05</v>
+        <v>0.002514081075787544</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.668660479481332e-05</v>
+        <v>0.009598272852599621</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.977797162719071e-05</v>
+        <v>0.008746574632823467</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0002096924145007506</v>
+        <v>0.006816748064011335</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.134802192216739e-05</v>
+        <v>0.004438946023583412</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.855773345800117e-05</v>
+        <v>0.01433852594345808</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.802418258506805e-05</v>
+        <v>0.004729014821350574</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.633686355897225e-05</v>
+        <v>0.0007465609814971685</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.0008793487795628607</v>
+        <v>0.04877177625894547</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.600180833833292e-05</v>
+        <v>0.005452296696603298</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.501353371073492e-05</v>
+        <v>0.009354183450341225</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0001536737545393407</v>
+        <v>0.01384487748146057</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.000222525472054258</v>
+        <v>0.01495853625237942</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.000217293098103255</v>
+        <v>3.765011206269264e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.733178138849325e-05</v>
+        <v>0.001302641001529992</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.511624188628048e-06</v>
+        <v>0.005791298113763332</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.0308378781192e-05</v>
+        <v>0.008024429902434349</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0003132105339318514</v>
+        <v>0.007456259801983833</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0001154878846136853</v>
+        <v>0.002959735225886106</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.817681524902582e-05</v>
+        <v>0.01019848510622978</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.000263370166067034</v>
+        <v>0.01244029588997364</v>
       </c>
       <c r="BH12" t="n">
-        <v>1.935460750246421e-05</v>
+        <v>0.000856718746945262</v>
       </c>
       <c r="BI12" t="n">
-        <v>7.423554052365944e-05</v>
+        <v>0.006081718020141125</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0002105586463585496</v>
+        <v>0.0144064873456955</v>
       </c>
       <c r="BK12" t="n">
-        <v>2.633206895552576e-05</v>
+        <v>0.006245409604161978</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0001709465286694467</v>
+        <v>0.002822359558194876</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0003969042154494673</v>
+        <v>0.009109021164476871</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0001165456342278048</v>
+        <v>0.01111082080751657</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.179668055963702e-05</v>
+        <v>0.01292276382446289</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0002545875322539359</v>
+        <v>0.01248304545879364</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.678339120000601e-05</v>
+        <v>0.004423889331519604</v>
       </c>
       <c r="BR12" t="n">
-        <v>8.313557191286236e-05</v>
+        <v>0.004828610923141241</v>
       </c>
       <c r="BS12" t="n">
-        <v>6.278074579313397e-05</v>
+        <v>0.002398591721430421</v>
       </c>
       <c r="BT12" t="n">
-        <v>3.215037941117771e-05</v>
+        <v>0.006592652760446072</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.072616841061972e-05</v>
+        <v>0.01091319043189287</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0005434128106571734</v>
+        <v>0.02896402776241302</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0002372300659772009</v>
+        <v>0.00678141787648201</v>
       </c>
       <c r="BX12" t="n">
-        <v>3.558948446880095e-05</v>
+        <v>0.003169101662933826</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.115346018807031e-05</v>
+        <v>0.00636074785143137</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0001451923308195546</v>
+        <v>0.001989996759220958</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.713008820544928e-05</v>
+        <v>0.009642003104090691</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.786301072570495e-05</v>
+        <v>0.006398580968379974</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.377217581146397e-05</v>
+        <v>0.003619306720793247</v>
       </c>
       <c r="CD12" t="n">
-        <v>9.562826562614646e-06</v>
+        <v>0.002658516634255648</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0002143941383110359</v>
+        <v>0.009820920415222645</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.064766092895297e-05</v>
+        <v>0.004559672903269529</v>
       </c>
       <c r="CG12" t="n">
-        <v>6.336042133625597e-05</v>
+        <v>0.001287723192945123</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.20594750114833e-05</v>
+        <v>0.003013828070834279</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.972488826140761e-05</v>
+        <v>0.004316110163927078</v>
       </c>
       <c r="CJ12" t="n">
-        <v>6.476586713688448e-05</v>
+        <v>0.0005086082965135574</v>
       </c>
       <c r="CK12" t="n">
-        <v>5.296926701703342e-06</v>
+        <v>0.001669074641540647</v>
       </c>
       <c r="CL12" t="n">
-        <v>3.009699139511213e-05</v>
+        <v>0.001821769983507693</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0002752371656242758</v>
+        <v>0.008083175867795944</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.00024825704167597</v>
+        <v>0.02605962939560413</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.109820914280135e-05</v>
+        <v>0.01068676263093948</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0001976561034098268</v>
+        <v>0.008732881397008896</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0003038596478290856</v>
+        <v>0.01865491643548012</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0001794474519556388</v>
+        <v>0.004822390154004097</v>
       </c>
       <c r="CS12" t="n">
-        <v>8.315009472426027e-05</v>
+        <v>0.003108486067503691</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0001286249898839742</v>
+        <v>0.002115848707035184</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.954713297891431e-06</v>
+        <v>0.001129017327912152</v>
       </c>
       <c r="CV12" t="n">
-        <v>6.566333468072116e-06</v>
+        <v>0.0005348559934645891</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0001743164320942014</v>
+        <v>0.009620112366974354</v>
       </c>
       <c r="CX12" t="n">
-        <v>5.069092730991542e-05</v>
+        <v>0.003382081864401698</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0001180257022497244</v>
+        <v>0.001490350812673569</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.276560735481326e-05</v>
+        <v>0.0006498598959296942</v>
       </c>
       <c r="DA12" t="n">
-        <v>4.56161615147721e-05</v>
+        <v>0.004568351898342371</v>
       </c>
       <c r="DB12" t="n">
-        <v>5.448361116577871e-05</v>
+        <v>0.003184362780302763</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.065574128413573e-05</v>
+        <v>0.0008658108999952674</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.22145226871362e-05</v>
+        <v>0.001475404482334852</v>
       </c>
       <c r="DE12" t="n">
-        <v>5.632701140712015e-05</v>
+        <v>0.001451241318136454</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0004638427635654807</v>
+        <v>0.0154256047680974</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.164632860512938e-05</v>
+        <v>0.01317339111119509</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0004018401668872684</v>
+        <v>0.01430524047464132</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0002391142188571393</v>
+        <v>0.001396988867782056</v>
       </c>
       <c r="DJ12" t="n">
-        <v>9.817979298532009e-05</v>
+        <v>0.01121959835290909</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0003092931874562055</v>
+        <v>0.00483601912856102</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0001300582953263074</v>
+        <v>0.006748320069164038</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0002963978331536055</v>
+        <v>0.01269714348018169</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0001167645386885852</v>
+        <v>0.001361775444820523</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.000230137724429369</v>
+        <v>0.007936536334455013</v>
       </c>
       <c r="DP12" t="n">
-        <v>5.918063106946647e-05</v>
+        <v>0.002596813021227717</v>
       </c>
       <c r="DQ12" t="n">
-        <v>6.671548180747777e-05</v>
+        <v>0.008976679295301437</v>
       </c>
       <c r="DR12" t="n">
-        <v>1.607453668839298e-05</v>
+        <v>0.002123650629073381</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0001675126695772633</v>
+        <v>0.0003727986477315426</v>
       </c>
       <c r="DT12" t="n">
-        <v>9.079716983251274e-05</v>
+        <v>0.001891158754006028</v>
       </c>
       <c r="DU12" t="n">
-        <v>2.836532439687289e-05</v>
+        <v>0.009897777810692787</v>
       </c>
       <c r="DV12" t="n">
-        <v>3.485685010673478e-05</v>
+        <v>0.004379881080240011</v>
       </c>
       <c r="DW12" t="n">
-        <v>3.603080403991044e-05</v>
+        <v>0.009189525619149208</v>
       </c>
       <c r="DX12" t="n">
-        <v>3.681640737340786e-05</v>
+        <v>0.009625013917684555</v>
       </c>
       <c r="DY12" t="n">
-        <v>1.239550965692615e-05</v>
+        <v>0.004467317834496498</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.50662594428286e-05</v>
+        <v>0.005259515251964331</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0001560039672767743</v>
+        <v>0.01154106296598911</v>
       </c>
       <c r="EB12" t="n">
-        <v>4.991485911887139e-05</v>
+        <v>0.009989203885197639</v>
       </c>
       <c r="EC12" t="n">
-        <v>5.606697959592566e-05</v>
+        <v>0.002069436479359865</v>
       </c>
       <c r="ED12" t="n">
-        <v>4.014605656266212e-05</v>
+        <v>0.007261168211698532</v>
       </c>
       <c r="EE12" t="n">
-        <v>8.536690438631922e-05</v>
+        <v>0.008374809287488461</v>
       </c>
       <c r="EF12" t="n">
-        <v>4.21092554461211e-05</v>
+        <v>0.006761349737644196</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0001020269119180739</v>
+        <v>0.003205467946827412</v>
       </c>
       <c r="EH12" t="n">
-        <v>3.144841684843414e-05</v>
+        <v>0.005950828548520803</v>
       </c>
       <c r="EI12" t="n">
-        <v>5.031004548072815e-05</v>
+        <v>0.008459209464490414</v>
       </c>
       <c r="EJ12" t="n">
-        <v>6.254874460864812e-05</v>
+        <v>8.89440270839259e-05</v>
       </c>
       <c r="EK12" t="n">
-        <v>8.802806405583397e-05</v>
+        <v>0.0001776143908500671</v>
       </c>
       <c r="EL12" t="n">
-        <v>8.408689609495923e-05</v>
+        <v>0.002794553292915225</v>
       </c>
       <c r="EM12" t="n">
-        <v>9.841369319474325e-07</v>
+        <v>0.000623299041762948</v>
       </c>
       <c r="EN12" t="n">
-        <v>6.289233169809449e-06</v>
+        <v>0.0009602861246094108</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0001325495395576581</v>
+        <v>0.01039037760347128</v>
       </c>
       <c r="EP12" t="n">
-        <v>2.923155625467189e-05</v>
+        <v>0.004980131983757019</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0001059439382515848</v>
+        <v>0.002799731213599443</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001546306593809277</v>
+        <v>0.01200676243752241</v>
       </c>
       <c r="ES12" t="n">
-        <v>9.410848724655807e-05</v>
+        <v>0.02033481746912003</v>
       </c>
       <c r="ET12" t="n">
-        <v>4.236232780385762e-05</v>
+        <v>0.0113575691357255</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0001006576494546607</v>
+        <v>0.009496112354099751</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.000102154808701016</v>
+        <v>0.002596847945824265</v>
       </c>
       <c r="EW12" t="n">
-        <v>7.421025657095015e-05</v>
+        <v>0.0009518862934783101</v>
       </c>
       <c r="EX12" t="n">
-        <v>4.464954145078082e-06</v>
+        <v>0.001109567936509848</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0001451082789571956</v>
+        <v>0.01199886854737997</v>
       </c>
       <c r="EZ12" t="n">
-        <v>1.608705133548938e-05</v>
+        <v>0.002999985823407769</v>
       </c>
       <c r="FA12" t="n">
-        <v>6.87174397171475e-05</v>
+        <v>0.001907057128846645</v>
       </c>
       <c r="FB12" t="n">
-        <v>4.990873276256025e-05</v>
+        <v>7.483526133000851e-06</v>
       </c>
       <c r="FC12" t="n">
-        <v>5.011980829294771e-05</v>
+        <v>0.004831224214285612</v>
       </c>
       <c r="FD12" t="n">
-        <v>9.012508962769061e-05</v>
+        <v>0.0004486037651076913</v>
       </c>
       <c r="FE12" t="n">
-        <v>4.942668056173716e-06</v>
+        <v>0.001997157232835889</v>
       </c>
       <c r="FF12" t="n">
-        <v>7.064511009957641e-05</v>
+        <v>0.002873301040381193</v>
       </c>
       <c r="FG12" t="n">
-        <v>2.01818547793664e-05</v>
+        <v>0.0008373791351914406</v>
       </c>
       <c r="FH12" t="n">
-        <v>9.661350486567244e-05</v>
+        <v>0.004812260158360004</v>
       </c>
       <c r="FI12" t="n">
-        <v>5.209697701502591e-05</v>
+        <v>0.001339937560260296</v>
       </c>
       <c r="FJ12" t="n">
-        <v>9.019566641654819e-05</v>
+        <v>0.01169036794453859</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.000114578302600421</v>
+        <v>0.01216194592416286</v>
       </c>
       <c r="FL12" t="n">
-        <v>5.715054794563912e-05</v>
+        <v>0.01261257007718086</v>
       </c>
       <c r="FM12" t="n">
-        <v>9.751621109899133e-05</v>
+        <v>0.006193613167852163</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0001240875863004476</v>
+        <v>0.01117035932838917</v>
       </c>
       <c r="FO12" t="n">
-        <v>2.753605986072216e-05</v>
+        <v>0.006983137223869562</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.000197309534996748</v>
+        <v>0.009497066028416157</v>
       </c>
       <c r="FQ12" t="n">
-        <v>6.033328827470541e-05</v>
+        <v>0.007641898468136787</v>
       </c>
       <c r="FR12" t="n">
-        <v>6.552255945280194e-05</v>
+        <v>0.005794408731162548</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0001664500014157966</v>
+        <v>0.008474881760776043</v>
       </c>
       <c r="FT12" t="n">
-        <v>1.381351466989145e-05</v>
+        <v>0.04189576953649521</v>
       </c>
       <c r="FU12" t="n">
-        <v>6.87690990162082e-05</v>
+        <v>0.005936305969953537</v>
       </c>
       <c r="FV12" t="n">
-        <v>1.623995012778323e-05</v>
+        <v>0.009793167002499104</v>
       </c>
       <c r="FW12" t="n">
-        <v>1.71897881955374e-05</v>
+        <v>0.01934101991355419</v>
       </c>
       <c r="FX12" t="n">
-        <v>7.320315489778295e-06</v>
+        <v>0.006094120442867279</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0001221097918460146</v>
+        <v>0.008604621514678001</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0001393414859194309</v>
+        <v>0.008770436979830265</v>
       </c>
       <c r="GA12" t="n">
-        <v>7.225329318316653e-05</v>
+        <v>0.003343768417835236</v>
       </c>
       <c r="GB12" t="n">
-        <v>1.766629611665849e-05</v>
+        <v>0.01297458168119192</v>
       </c>
       <c r="GC12" t="n">
-        <v>8.74191609909758e-05</v>
+        <v>0.003258340526372194</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0001879635965451598</v>
+        <v>0.001555693568661809</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0001683218142716214</v>
+        <v>0.007771255914121866</v>
       </c>
       <c r="GF12" t="n">
-        <v>7.514718163292855e-07</v>
+        <v>0.01236048340797424</v>
       </c>
       <c r="GG12" t="n">
-        <v>6.46921107545495e-05</v>
+        <v>0.005271967500448227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0003530065005179495</v>
+        <v>0.1359681189060211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.005732037127017975</v>
+        <v>0.04251937940716743</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0003909642982762307</v>
+        <v>0.04732752963900566</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003212523646652699</v>
+        <v>0.5968475341796875</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002129185246303678</v>
+        <v>0.09571951627731323</v>
       </c>
       <c r="F13" t="n">
-        <v>5.403459363151342e-05</v>
+        <v>0.1336358487606049</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0008018409134820104</v>
+        <v>0.2373519241809845</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0009095708373934031</v>
+        <v>0.1525599360466003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0003245011321268976</v>
+        <v>0.02156979590654373</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002957389806397259</v>
+        <v>0.1782177686691284</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004156108014285564</v>
+        <v>0.04800154641270638</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0005660675233229995</v>
+        <v>0.01532262191176414</v>
       </c>
       <c r="M13" t="n">
-        <v>0.002449214225634933</v>
+        <v>0.7764351367950439</v>
       </c>
       <c r="N13" t="n">
-        <v>0.002409079810604453</v>
+        <v>0.08810267597436905</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0006962275947444141</v>
+        <v>0.2175536751747131</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000771515944506973</v>
+        <v>0.2662820219993591</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0002686039661057293</v>
+        <v>0.03369370847940445</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0003278217918705195</v>
+        <v>0.07560627162456512</v>
       </c>
       <c r="S13" t="n">
-        <v>9.816017700359225e-05</v>
+        <v>0.0001548725413158536</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001001554192043841</v>
+        <v>0.03344807028770447</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0004169469757471234</v>
+        <v>0.01650909334421158</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0007240825798362494</v>
+        <v>0.05178805440664291</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0005343552911654115</v>
+        <v>0.1224657297134399</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0007271122885867953</v>
+        <v>0.1310380399227142</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0005480788531713188</v>
+        <v>0.0148204043507576</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0007042006473056972</v>
+        <v>0.02016669698059559</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0005307401879690588</v>
+        <v>0.02944475039839745</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0001580228563398123</v>
+        <v>0.0008914628997445107</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0008381317020393908</v>
+        <v>0.01400845870375633</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0003756016376428306</v>
+        <v>0.03772541135549545</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0007934908499009907</v>
+        <v>0.03995935618877411</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.000134811969473958</v>
+        <v>0.01996494829654694</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0002416907227598131</v>
+        <v>0.1311048269271851</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.000207092976779677</v>
+        <v>0.05853958427906036</v>
       </c>
       <c r="AI13" t="n">
-        <v>8.500099647790194e-05</v>
+        <v>0.0262234415858984</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0004738155694212765</v>
+        <v>0.1618537455797195</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0001384484639856964</v>
+        <v>0.06300608813762665</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0007613615016452968</v>
+        <v>0.09267458319664001</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0005154475220479071</v>
+        <v>0.005556400865316391</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.003746916074306e-05</v>
+        <v>0.09519711881875992</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0006524948985315859</v>
+        <v>0.03906599059700966</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0005929362378083169</v>
+        <v>0.1180385947227478</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0003844296443276107</v>
+        <v>0.1504899114370346</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0005496960948221385</v>
+        <v>0.007946017198264599</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0001870337291620672</v>
+        <v>0.02233466878533363</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0005189873045310378</v>
+        <v>0.0905187577009201</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.004202707204967737</v>
+        <v>0.04672854393720627</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.677069227909669e-05</v>
+        <v>0.06440803408622742</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0004769078223034739</v>
+        <v>0.277957558631897</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0007343284669332206</v>
+        <v>0.2893882989883423</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.179417247651145e-05</v>
+        <v>0.1312947869300842</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0001321600284427404</v>
+        <v>0.01983782649040222</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0003019240102730691</v>
+        <v>0.04544510319828987</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.254997550859116e-05</v>
+        <v>0.1072151884436607</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0004930377472192049</v>
+        <v>0.01635568030178547</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.001155687845312059</v>
+        <v>0.006597334519028664</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0006122726481407881</v>
+        <v>0.01983563043177128</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0006307856529019773</v>
+        <v>4.13060188293457e-05</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.001595758949406445</v>
+        <v>0.1540942490100861</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0002197191788582131</v>
+        <v>0.0217594038695097</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0008814072934910655</v>
+        <v>0.08442153036594391</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0005805437103845179</v>
+        <v>0.1321651637554169</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0001581263350090012</v>
+        <v>0.128142774105072</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0007860578480176628</v>
+        <v>0.02081243135035038</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0015741977840662</v>
+        <v>0.006616247817873955</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0006955850985832512</v>
+        <v>0.04211001470685005</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0001230650814250112</v>
+        <v>0.08293448388576508</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0003814151277765632</v>
+        <v>0.02863135188817978</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0006866919575259089</v>
+        <v>0.0407542772591114</v>
       </c>
       <c r="BR13" t="n">
-        <v>1.549598528072238e-05</v>
+        <v>0.009638975374400616</v>
       </c>
       <c r="BS13" t="n">
-        <v>4.284915485186502e-05</v>
+        <v>0.03614440560340881</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0002845702401828021</v>
+        <v>0.02414718270301819</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0006019703578203917</v>
+        <v>0.05311070382595062</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.002618169644847512</v>
+        <v>0.002239085733890533</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.000570296891964972</v>
+        <v>0.01591338962316513</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0005085293669253588</v>
+        <v>0.290482759475708</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0001463718945160508</v>
+        <v>0.1174072176218033</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.001247805776074529</v>
+        <v>0.1381924748420715</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0002683256170712411</v>
+        <v>0.003220736980438232</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0002175649715354666</v>
+        <v>0.03569648042321205</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0006706035928800702</v>
+        <v>0.02694506943225861</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0001773934927769005</v>
+        <v>0.07789693027734756</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0008598202257417142</v>
+        <v>0.009808240458369255</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.000171559484442696</v>
+        <v>0.001745507586747408</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0004110552836209536</v>
+        <v>0.2014849185943604</v>
       </c>
       <c r="CH13" t="n">
-        <v>8.749779954086989e-05</v>
+        <v>0.0019624806009233</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0001600848918315023</v>
+        <v>0.03412327170372009</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0002058388199657202</v>
+        <v>0.002384355291724205</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.961087036761455e-05</v>
+        <v>0.07148773223161697</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0002418739895801991</v>
+        <v>0.002955883974209428</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0008559239213354886</v>
+        <v>0.08947820961475372</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0007495501195080578</v>
+        <v>0.03861205652356148</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0001993134937947616</v>
+        <v>0.1736340820789337</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.000771219318266958</v>
+        <v>0.3229489922523499</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0006198749761097133</v>
+        <v>0.1285945475101471</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0005882256082259119</v>
+        <v>0.003398020751774311</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0008286327356472611</v>
+        <v>0.05070409923791885</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.001557893352583051</v>
+        <v>0.1148467883467674</v>
       </c>
       <c r="CU13" t="n">
-        <v>6.800724077038467e-05</v>
+        <v>0.06866700202226639</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0002278033352922648</v>
+        <v>0.0759395956993103</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0006248597637750208</v>
+        <v>0.002842510584741831</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0003558957250788808</v>
+        <v>0.01837621256709099</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0006984462379477918</v>
+        <v>0.2186273038387299</v>
       </c>
       <c r="CZ13" t="n">
-        <v>4.435711889527738e-05</v>
+        <v>0.01762638613581657</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0002152387896785513</v>
+        <v>0.03696103394031525</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0001730510994093493</v>
+        <v>0.01920868456363678</v>
       </c>
       <c r="DC13" t="n">
-        <v>7.346313213929534e-05</v>
+        <v>0.05712942034006119</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.340543768601492e-05</v>
+        <v>0.01070951577275991</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0001767947396729141</v>
+        <v>0.05035196989774704</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.001208521774969995</v>
+        <v>0.03155108541250229</v>
       </c>
       <c r="DG13" t="n">
-        <v>9.781776316231117e-05</v>
+        <v>0.04361885040998459</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.001772149698808789</v>
+        <v>0.1409608721733093</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0002448449959047139</v>
+        <v>0.1084839478135109</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0007083003292791545</v>
+        <v>0.004167456179857254</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0009067218634299934</v>
+        <v>0.01073227077722549</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0003757932281587273</v>
+        <v>0.3234054148197174</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0001488963316660374</v>
+        <v>0.03615027293562889</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.000541982997674495</v>
+        <v>0.01836322993040085</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0002564784663263708</v>
+        <v>0.01841448061168194</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0003479219740256667</v>
+        <v>0.04729017615318298</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0001144898706115782</v>
+        <v>0.08170730620622635</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0004449583357200027</v>
+        <v>0.03221011534333229</v>
       </c>
       <c r="DS13" t="n">
-        <v>8.854065526975319e-06</v>
+        <v>0.06725915521383286</v>
       </c>
       <c r="DT13" t="n">
-        <v>7.932471635285765e-05</v>
+        <v>0.0574822835624218</v>
       </c>
       <c r="DU13" t="n">
-        <v>9.254092583432794e-05</v>
+        <v>0.07033207267522812</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0002302795473951846</v>
+        <v>0.2031344473361969</v>
       </c>
       <c r="DW13" t="n">
-        <v>1.574855195940472e-05</v>
+        <v>0.01293857023119926</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0001428618561476469</v>
+        <v>0.01199925970286131</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.000195815839106217</v>
+        <v>0.1237156391143799</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.274340269854292e-05</v>
+        <v>0.08700338006019592</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0009066041093319654</v>
+        <v>0.04818090796470642</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0004125361447222531</v>
+        <v>0.01765162870287895</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0002085004962282255</v>
+        <v>0.02340984903275967</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0002368604764342308</v>
+        <v>0.2091771215200424</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0001068370038410649</v>
+        <v>0.1433336287736893</v>
       </c>
       <c r="EF13" t="n">
-        <v>6.689841393381357e-05</v>
+        <v>0.1455821990966797</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0005897833034396172</v>
+        <v>0.0258894432336092</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0001995719503611326</v>
+        <v>0.0385749340057373</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0002947829489130527</v>
+        <v>0.1938672065734863</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0007717855623923242</v>
+        <v>0.04114549234509468</v>
       </c>
       <c r="EK13" t="n">
-        <v>4.160738535574637e-05</v>
+        <v>0.0338212326169014</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0001111571255023591</v>
+        <v>0.005526226013898849</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0001648634643061087</v>
+        <v>0.05044276639819145</v>
       </c>
       <c r="EN13" t="n">
-        <v>6.563066563103348e-05</v>
+        <v>0.01346527226269245</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0002804092946462333</v>
+        <v>0.02278570644557476</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0001907326804939657</v>
+        <v>0.05383207648992538</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0004952558665536344</v>
+        <v>0.02409909851849079</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0008742493810132146</v>
+        <v>0.1806285977363586</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0003354148066136986</v>
+        <v>0.06076870113611221</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.001005616621114314</v>
+        <v>0.1317688971757889</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0004136383649893105</v>
+        <v>0.1010846719145775</v>
       </c>
       <c r="EV13" t="n">
-        <v>1.409987089573406e-05</v>
+        <v>0.06884671747684479</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0001976657367777079</v>
+        <v>0.2381985634565353</v>
       </c>
       <c r="EX13" t="n">
-        <v>9.195115126203746e-05</v>
+        <v>0.07668565213680267</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0006391842034645379</v>
+        <v>0.009042559191584587</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0002635153068695217</v>
+        <v>0.006253281608223915</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.000655258831102401</v>
+        <v>0.2421787977218628</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0001233287184732035</v>
+        <v>0.004545621573925018</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0003156817401759326</v>
+        <v>0.007948294281959534</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0003230612492188811</v>
+        <v>0.03113438561558723</v>
       </c>
       <c r="FE13" t="n">
-        <v>1.472133953939192e-05</v>
+        <v>0.07762620598077774</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0002399887162027881</v>
+        <v>0.00121380016207695</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0002304896770510823</v>
+        <v>0.01866098865866661</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0003725539136212319</v>
+        <v>0.03189629688858986</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0002119382406817749</v>
+        <v>0.04775334149599075</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0005432516918517649</v>
+        <v>0.06223152577877045</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0003542247868608683</v>
+        <v>0.0872792974114418</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0002259440952911973</v>
+        <v>0.02843879535794258</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0001544467522762716</v>
+        <v>0.0361223965883255</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0002758215414360166</v>
+        <v>0.01641157083213329</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0001861748314695433</v>
+        <v>0.05697939917445183</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0004174676141701639</v>
+        <v>0.08425906300544739</v>
       </c>
       <c r="FQ13" t="n">
-        <v>5.056450754636899e-05</v>
+        <v>0.08097198605537415</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.000851536518894136</v>
+        <v>0.1165818497538567</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0002348052948946133</v>
+        <v>0.2151045054197311</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0001429190597264096</v>
+        <v>0.01685982197523117</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0004236228996887803</v>
+        <v>0.03221669420599937</v>
       </c>
       <c r="FV13" t="n">
-        <v>6.145254155853763e-05</v>
+        <v>0.02709903195500374</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0003754997160285711</v>
+        <v>0.3238645195960999</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0003046073252335191</v>
+        <v>0.0071797757409513</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0005804095417261124</v>
+        <v>0.0631159245967865</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0001419460168108344</v>
+        <v>0.003927403129637241</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0004193458007648587</v>
+        <v>0.04344509541988373</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.000413610425312072</v>
+        <v>0.23263880610466</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0003285341081209481</v>
+        <v>0.006066882982850075</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.001112289261072874</v>
+        <v>0.04440721124410629</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.001706038485281169</v>
+        <v>0.2132809460163116</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0003219458449166268</v>
+        <v>0.003487005829811096</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0001114153055823408</v>
+        <v>0.1201844960451126</v>
       </c>
     </row>
   </sheetData>
